--- a/docs/xlsx/jobs-2026-09-30.xlsx
+++ b/docs/xlsx/jobs-2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="621">
   <si>
     <t>Title</t>
   </si>
@@ -40,6 +40,1509 @@
     <t>Link</t>
   </si>
   <si>
+    <t>2027 VNRC / VCV / VPA Legislative Intern</t>
+  </si>
+  <si>
+    <t>Vermont Natural Resources Council</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$18.50 per hour</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-vnrc--vcv--vpa-legislative-intern-montpelier-vermont/3379646539</t>
+  </si>
+  <si>
+    <t>Acquisition Assistant</t>
+  </si>
+  <si>
+    <t>Sonoma County Ag + Open Space</t>
+  </si>
+  <si>
+    <t>Santa Rosa, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$96,341.46 - $117,087.43 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-acquisition-assistant-santa-rosa-california/5639525180</t>
+  </si>
+  <si>
+    <t>Archaeology Crew Lead (NPS, Death Valley National Park)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Death Valley, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$27.50 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeology-crew-lead-nps-death-valley-national-park-death-valley-california/5236350349</t>
+  </si>
+  <si>
+    <t>Archaeology Crew Member (NPS, Death Valley National Park)</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeology-crew-member-nps-death-valley-national-park-death-valley-california/5618656529</t>
+  </si>
+  <si>
+    <t>Archaeology Technician IV (NPS, Yellowstone NP)</t>
+  </si>
+  <si>
+    <t>Gardiner, MT</t>
+  </si>
+  <si>
+    <t>$24.18 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-archaeology-technician-iv-nps-yellowstone-np-gardiner-montana/4017282276</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Oklahoma Biological Survey and Biological Sciences- Vector Biology and One Health (Tenure-Track)</t>
+  </si>
+  <si>
+    <t>University of Oklahoma</t>
+  </si>
+  <si>
+    <t>Norman, OK</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Salary is competitive and commensurate with rank and experience</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-of-oklahoma-biological-survey-and-biological-sciences--vector-biology-and-one-health-tenure-track-norman-oklahoma/7848276584</t>
+  </si>
+  <si>
+    <t>Ballast Water Vessel Inspector - Marine Transportation and Safety Specialist 3 - Perm - 2026-08084</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Ridgefield, WA</t>
+  </si>
+  <si>
+    <t>$7,044 - $9,478 per month</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ballast-water-vessel-inspector---marine-transportation-and-safety-specialist-3---perm---2026-08084-ridgefield-washington/6219401301</t>
+  </si>
+  <si>
+    <t>CELP Program Director</t>
+  </si>
+  <si>
+    <t>Catalina Island Camps</t>
+  </si>
+  <si>
+    <t>Two Harbors, CA</t>
+  </si>
+  <si>
+    <t>$72,500 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-celp-program-director-two-harbors-california/4469608111</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy - Minnesota Northwoods</t>
+  </si>
+  <si>
+    <t>Trust for Public Land</t>
+  </si>
+  <si>
+    <t>St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$130,000 - $145,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-philanthropy---minnesota-northwoods-st-paul-minnesota/8070005886</t>
+  </si>
+  <si>
+    <t>Education and Science Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>University of California Santa Barbara</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>$66,798 - $83,469 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-and-science-engagement-coordinator-los-angeles-california/1043398125</t>
+  </si>
+  <si>
+    <t>Emerging Leaders for Climate Action Fellowship</t>
+  </si>
+  <si>
+    <t>Globally</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-emerging-leaders-for-climate-action-fellowship-washington-dc/9848183429</t>
+  </si>
+  <si>
+    <t>Environmental Education Program Coordinator</t>
+  </si>
+  <si>
+    <t>Fortson 4-H Center - University of Georgia</t>
+  </si>
+  <si>
+    <t>Hampton, GA</t>
+  </si>
+  <si>
+    <t>$40,000 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-program-coordinator-hampton-georgia/8311418968</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Amargosa Conservancy</t>
+  </si>
+  <si>
+    <t>Las Vegas, NV</t>
+  </si>
+  <si>
+    <t>$115,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-las-vegas-nevada/2560812771</t>
+  </si>
+  <si>
+    <t>Fuels Program Manager</t>
+  </si>
+  <si>
+    <t>Trinity County Resource Conservation District</t>
+  </si>
+  <si>
+    <t>Weaverville, CA</t>
+  </si>
+  <si>
+    <t>$36 - $41.67 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fuels-program-manager-weaverville-california/2002826213</t>
+  </si>
+  <si>
+    <t>Intern/Teacher/Naturalist Year-long Paid Internship</t>
+  </si>
+  <si>
+    <t>Jay C. Hormel Nature Center</t>
+  </si>
+  <si>
+    <t>Austin, MN</t>
+  </si>
+  <si>
+    <t>$15.50 - $16 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-internteachernaturalist-year-long-paid-internship-austin-minnesota/1583763046</t>
+  </si>
+  <si>
+    <t>Maintenance Supervisor</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-supervisor-two-harbors-california/9219422074</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist – Permitting Specialist</t>
+  </si>
+  <si>
+    <t>CEHMM</t>
+  </si>
+  <si>
+    <t>Carlsbad, NM</t>
+  </si>
+  <si>
+    <t>$25 - $35 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist--permitting-specialist-carlsbad-new-mexico/7410734038</t>
+  </si>
+  <si>
+    <t>Outdoor Programs Manager</t>
+  </si>
+  <si>
+    <t>Nashua River Watershed Association</t>
+  </si>
+  <si>
+    <t>Groton, MA</t>
+  </si>
+  <si>
+    <t>$57,000 - $63,000 per year</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-programs-manager-groton-massachusetts/6398991632</t>
+  </si>
+  <si>
+    <t>Part-time Marketing and Membership Administrator</t>
+  </si>
+  <si>
+    <t>Green Newton</t>
+  </si>
+  <si>
+    <t>Newton, MA</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-part-time-marketing-and-membership-administrator-newton-massachusetts/8236857419</t>
+  </si>
+  <si>
+    <t>Postdoctoral Associate – Forest Futures Lab/Western Fire and Forest Resilience Collaborative</t>
+  </si>
+  <si>
+    <t>Cary Institute of Ecosystem Studies</t>
+  </si>
+  <si>
+    <t>Millbrook, NY</t>
+  </si>
+  <si>
+    <t>$74,263 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-associate--forest-futures-labwestern-fire-and-forest-resilience-collaborative-millbrook-new-york/3120306392</t>
+  </si>
+  <si>
+    <t>Project Forester</t>
+  </si>
+  <si>
+    <t>New Mexico Forestry Division</t>
+  </si>
+  <si>
+    <t>Tierra Amarilla, NM</t>
+  </si>
+  <si>
+    <t>$56,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-forester-tierra-amarilla-new-mexico/6277120089</t>
+  </si>
+  <si>
+    <t>Regional Trails Manager</t>
+  </si>
+  <si>
+    <t>Triangle Off-Road Cyclists (TORC)</t>
+  </si>
+  <si>
+    <t>Greater Triangle, NC</t>
+  </si>
+  <si>
+    <t>$60,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regional-trails-manager-greater-triangle-north-carolina/1100040216</t>
+  </si>
+  <si>
+    <t>Senior Environmental Scientist (Specialist)</t>
+  </si>
+  <si>
+    <t>California Department of Fish and Wildlife Native Plant Program</t>
+  </si>
+  <si>
+    <t>West Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$7,820 - $10,732 per month</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-environmental-scientist-specialist-west-sacramento-california/4914501818</t>
+  </si>
+  <si>
+    <t>Sierra Nevada Yellow-Legged Frog Project Manager</t>
+  </si>
+  <si>
+    <t>Plumas Audubon Society</t>
+  </si>
+  <si>
+    <t>Quincy, CA</t>
+  </si>
+  <si>
+    <t>$25 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sierra-nevada-yellow-legged-frog-project-manager-quincy-california/5111881542</t>
+  </si>
+  <si>
+    <t>Temporary Field Assistant</t>
+  </si>
+  <si>
+    <t>Harvard University/HUH and OEB</t>
+  </si>
+  <si>
+    <t>Petersham, MA</t>
+  </si>
+  <si>
+    <t>$19 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-temporary-field-assistant-petersham-massachusetts/1678404751</t>
+  </si>
+  <si>
+    <t>Water Agency Senior Environmental Specialist - Tribal Liaison</t>
+  </si>
+  <si>
+    <t>County of Sonoma, Human Resources Dept.</t>
+  </si>
+  <si>
+    <t>$115,167.28 - $139,983.14 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-agency-senior-environmental-specialist---tribal-liaison-santa-rosa-california/5669874213</t>
+  </si>
+  <si>
+    <t>Wildland Fire Fuels Crew Member</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Deer Park, WA</t>
+  </si>
+  <si>
+    <t>$3,565 - $4,746 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-fuels-crew-member-deer-park-washington/4162646200</t>
+  </si>
+  <si>
+    <t>Wildland Fire Hand Crew Squad Boss</t>
+  </si>
+  <si>
+    <t>Yakima, WA</t>
+  </si>
+  <si>
+    <t>$3,827 - $5,111 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-hand-crew-squad-boss-yakima-washington/7455993015</t>
+  </si>
+  <si>
+    <t>Wildland Fire Management Lead</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-management-lead-deer-park-washington/3172345433</t>
+  </si>
+  <si>
+    <t>Wildland Fire Management Supervisor</t>
+  </si>
+  <si>
+    <t>$4,201 - $5,642 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-management-supervisor-deer-park-washington/9324844249</t>
+  </si>
+  <si>
+    <t>Administrative Organizer - Union Representative - Gold Coast Region</t>
+  </si>
+  <si>
+    <t>1199 SEIU United Healthcare Workers East</t>
+  </si>
+  <si>
+    <t>Miramar, Florida</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 81000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a0eb693927ea4aacba4e0f2cd1319b38-administrative-organizer-union-representative-gold-coast-region-1199-seiu-united-healthcare-workers-east-miramar</t>
+  </si>
+  <si>
+    <t>Administrative Organizer - Union Representative - HCA Area</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d67b366acc8841b99cefca86d5bf316f-administrative-organizer-union-representative-hca-area-1199-seiu-united-healthcare-workers-east-miramar</t>
+  </si>
+  <si>
+    <t>Administrative Organizer - Union Representative - Tenet</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Job Workplace, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e087bce1a794a369f5fabec5e85999b-administrative-organizer-union-representative-tenet-1199-seiu-united-healthcare-workers-east-miramar</t>
+  </si>
+  <si>
+    <t>Administrative Specialist - Social Services and Business Administration</t>
+  </si>
+  <si>
+    <t>The Salvation Army National Headquarters</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 30.92 - 40.13/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a55d8a3c6cd4623bc8dfda50086fbad-administrative-specialist-social-services-and-business-administration-the-salvation-army-national-headquarters-alexandria</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/ad3fe370dbea4cbfb0735900f14395f6-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant Camp Director</t>
+  </si>
+  <si>
+    <t>The AnBryce Foundation</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/113efd531ac8400798b6a0a228aba8ea-assistant-camp-director-the-anbryce-foundation-washington</t>
+  </si>
+  <si>
+    <t>Assistant Warehouse Manager</t>
+  </si>
+  <si>
+    <t>State College Food Bank</t>
+  </si>
+  <si>
+    <t>State College, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2c4646f214f4b3cad23c228847d2a69-assistant-warehouse-manager-state-college-food-bank-state-college</t>
+  </si>
+  <si>
+    <t>Associate Director of Annual Giving for Campus Partnerships &amp; Digital Campaigns</t>
+  </si>
+  <si>
+    <t>University of Vermont Foundation</t>
+  </si>
+  <si>
+    <t>Burlington, Vermont</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1dc86d330e1a4f86bbd0681724f9b292-associate-director-of-annual-giving-for-campus-partnerships-digital-campaigns-university-of-vermont-foundation-burlington</t>
+  </si>
+  <si>
+    <t>Associate Director, Education Policy, CEA Flexible within the US: South or Midwest Preferred</t>
+  </si>
+  <si>
+    <t>AJC</t>
+  </si>
+  <si>
+    <t>Remote (New York, New York)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/243787d2142141bd8f07c756c4782a55-associate-director-education-policy-cea-flexible-within-the-us-south-or-midwest-preferred-ajc-new-york</t>
+  </si>
+  <si>
+    <t>ATTAIN Lab Coordinator, NYC - Staten Island</t>
+  </si>
+  <si>
+    <t>The Research Foundation For SUNY</t>
+  </si>
+  <si>
+    <t>Staten Island, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/76dd1d5e018c4e528793444c3d927f50-attain-lab-coordinator-nyc-staten-island-the-research-foundation-for-suny-staten-island</t>
+  </si>
+  <si>
+    <t>Brooklyn Regional Director, AG’s Intergovernmental Affairs (6462)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90836.00 - 90836.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d033ebf6eb7741eb9573533b180d1644-brooklyn-regional-director-ags-intergovernmental-affairs-6462-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Campus Operations Assistant/College Assistant</t>
+  </si>
+  <si>
+    <t>CUNY School of Professional Studies</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/098edce5c291415385dec89e13db24c4-campus-operations-assistantcollege-assistant-cuny-school-of-professional-studies-new-york</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer | Young Moms Together</t>
+  </si>
+  <si>
+    <t>Capital Development Services</t>
+  </si>
+  <si>
+    <t>Charleston, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Family, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1c2fb692274b42dfaa6b1cd3aecef234-chief-executive-officer-young-moms-together-capital-development-services-charleston</t>
+  </si>
+  <si>
+    <t>Chief Financial and Administrative Officer</t>
+  </si>
+  <si>
+    <t>The Clean Slate Initiative</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 260000.00/year</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ba68ff719c254f50bf30d5ebb9af6170-chief-financial-and-administrative-officer-the-clean-slate-initiative-orlando</t>
+  </si>
+  <si>
+    <t>Coastal Reporter-Producer</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>Remote (Oregon)</t>
+  </si>
+  <si>
+    <t>USD 36.09 - 36.09/hour</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ce475d365224a24b256582ac46d5d18-coastal-reporter-producer-opb-portland</t>
+  </si>
+  <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Mid-Atlantic Innocence Project</t>
+  </si>
+  <si>
+    <t>USD 47700.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55dc64606ee543fcbddf73c91e86adc9-communications-associate-mid-atlantic-innocence-project-washington</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>CAIR San Francisco Bay Area</t>
+  </si>
+  <si>
+    <t>Santa Clara, CA</t>
+  </si>
+  <si>
+    <t>USD 92888.00 - 116086.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b91b0c6c0d74cb0a189c9b7f4baf143-community-engagement-manager-cair-san-francisco-bay-area-santa-clara</t>
+  </si>
+  <si>
+    <t>Community Outreach Rep. (Sustainability + Nutrition) - Portland</t>
+  </si>
+  <si>
+    <t>Full Circle</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 34650.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/8a0a36010b6644e485dd8b593e96ef35-community-outreach-rep-sustainability-nutrition-portland-full-circle-portland</t>
+  </si>
+  <si>
+    <t>Coordinator, CE Provider Approval</t>
+  </si>
+  <si>
+    <t>American Speech-Language-Hearing Association</t>
+  </si>
+  <si>
+    <t>Rockville, MD</t>
+  </si>
+  <si>
+    <t>USD 61115.00 - 67905.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1aee0f2eadc347c69a8df1094cf86bb9-coordinator-ce-provider-approval-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>CTUL - Executive Director</t>
+  </si>
+  <si>
+    <t>Centro de Trabajadores Unidos En Lucha (CTUL)</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d0faafabb8d40c6a730a29bc683c876-ctul-executive-director-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
+    <t>Day Labor Lead Organizer</t>
+  </si>
+  <si>
+    <t>Street Level Health Project</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c52002d54e2441da51b5af34b625d7e-day-labor-lead-organizer-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>Asian Arts Initiative of Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 65520.00 - 65520.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8673ddadf02a42fa81c39d407fb1e7b3-development-coordinator-asian-arts-initiative-of-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Development Database &amp; Reporting Coordinator</t>
+  </si>
+  <si>
+    <t>The Cathedral Church of Saint John the Divine of New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 42.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/671a5721ff71449096ec8c0253adaeb8-development-database-reporting-coordinator-the-cathedral-church-of-saint-john-the-divine-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Development Gift Processing &amp; Acknowledgement Coordinator</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe182ed433e04b97bc8a85eefd9ffd37-development-gift-processing-acknowledgement-coordinator-the-cathedral-church-of-saint-john-the-divine-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Development Officer</t>
+  </si>
+  <si>
+    <t>Judge Baker Children's Center dba The Baker Center for Children and Families</t>
+  </si>
+  <si>
+    <t>Waltham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1551982d38ae44ef83a81f0ef522822d-development-officer-judge-baker-childrens-center-dba-the-baker-center-for-children-and-families-waltham</t>
+  </si>
+  <si>
+    <t>Digital Content Coordinator</t>
+  </si>
+  <si>
+    <t>Cookies for Kids' Cancer</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a77e187d7f2c4834a8990301e06ce65f-digital-content-coordinator-cookies-for-kids-cancer-new-york</t>
+  </si>
+  <si>
+    <t>Digital Marketing &amp; Design Manager</t>
+  </si>
+  <si>
+    <t>Holy Apostles Soup Kitchen</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a91d30decc04472497308522a5688399-digital-marketing-design-manager-holy-apostles-soup-kitchen-new-york</t>
+  </si>
+  <si>
+    <t>Digital Resource Manager</t>
+  </si>
+  <si>
+    <t>Faunalytics</t>
+  </si>
+  <si>
+    <t>USD 68900.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3b21ef13d704c7bbabf942b9848c13c-digital-resource-manager-faunalytics-olympia</t>
+  </si>
+  <si>
+    <t>Director of Digital and Movement Building</t>
+  </si>
+  <si>
+    <t>Center for Countering Digital Hate</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35ef1f3490ec43ee9c46c7d2637f57e9-director-of-digital-and-movement-building-center-for-countering-digital-hate-washington</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Los Angeles Neighborhood Land Trust</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 135000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/878d7eb99fc2461aa6b83af43a2ac9e3-director-of-finance-los-angeles-neighborhood-land-trust-los-angeles</t>
+  </si>
+  <si>
+    <t>USD 94760.00 - 94760.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73289675cf4c4ac291d74e5858ad9db9-director-of-finance-asian-arts-initiative-of-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>LEAP for Education Inc.</t>
+  </si>
+  <si>
+    <t>Salem, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90812.00 - 112486.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce90a7b47f8d4152b183bb0cc322959e-director-of-finance-and-operations-leap-for-education-inc-salem</t>
+  </si>
+  <si>
+    <t>Director of Social Services (Queens)</t>
+  </si>
+  <si>
+    <t>Housing Solutions of New York</t>
+  </si>
+  <si>
+    <t>Queens, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Women, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/41dbe71e4f524110b4ac338203005608-director-of-social-services-queens-housing-solutions-of-new-york-queens</t>
+  </si>
+  <si>
+    <t>Director of Strategic Philanthropy</t>
+  </si>
+  <si>
+    <t>Hamilton Families</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9a0ee6f2c054174a97e7a4aed28af89-director-of-strategic-philanthropy-hamilton-families-san-francisco</t>
+  </si>
+  <si>
+    <t>Environmental Educator</t>
+  </si>
+  <si>
+    <t>Christodora: Nature, Learning, Leadership</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 600.00 - 600.00/week</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7fa71c20e654c24adedc28319be5346-environmental-educator-christodora-nature-learning-leadership-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant</t>
+  </si>
+  <si>
+    <t>Scale to Win</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/7380673820c146edada87bfb25dee514-executive-assistant-scale-to-win-santa-ana</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the Senior Pastor/Head of Staff</t>
+  </si>
+  <si>
+    <t>Fourth Presbyterian Church of Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ec60ddbb07cf4a1e80b74f4ef1706685-executive-assistant-to-the-senior-pastorhead-of-staff-fourth-presbyterian-church-of-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Executive Associate</t>
+  </si>
+  <si>
+    <t>The One America Movement</t>
+  </si>
+  <si>
+    <t>Bowie, Maryland</t>
+  </si>
+  <si>
+    <t>USD 52800.00 - 68600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6048c652bcd44d43b9d43ccfef8e0ce8-executive-associate-the-one-america-movement-bowie</t>
+  </si>
+  <si>
+    <t>PEN/ Faulkner Foundation</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33573dc019b34d178bcc5ede8e7689c2-executive-director-pen-faulkner-foundation-washington</t>
+  </si>
+  <si>
+    <t>William A Harrison Jr Foundation</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f52734dd63e64c65acf4524898c2c2d6-executive-director-william-a-harrison-jr-foundation-richmond</t>
+  </si>
+  <si>
+    <t>Executive Director / Head of U.S. Operations - Friends of The Buddha Fellows</t>
+  </si>
+  <si>
+    <t>Equal Innovation</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/d194fa5ca99346978900fd3cdd0b69c8-executive-director-head-of-us-operations-friends-of-the-buddha-fellows-equal-innovation-boston</t>
+  </si>
+  <si>
+    <t>Facilitator</t>
+  </si>
+  <si>
+    <t>National Cares Mentoring Movement</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 0.00 - 70.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4976be9f0a9419c9b2c6ac578f68a65-facilitator-national-cares-mentoring-movement-new-york</t>
+  </si>
+  <si>
+    <t>Farm and Forest Viability Program Coordinator</t>
+  </si>
+  <si>
+    <t>Vermont Housing &amp; Conservation Board</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/75ce2c56e9e84493acaa08acfb110c0a-farm-and-forest-viability-program-coordinator-vermont-housing-conservation-board-montpelier</t>
+  </si>
+  <si>
+    <t>Finance Coordinator</t>
+  </si>
+  <si>
+    <t>Tennessee Immigrant and Refugee Rights Coalition</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88e7ac17c3414522ba05de1a35acf979-finance-coordinator-tennessee-immigrant-and-refugee-rights-coalition-nashville</t>
+  </si>
+  <si>
+    <t>Finance Director</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/124a8efa82f04da0be0a2f8720c3c510-finance-director-tennessee-immigrant-and-refugee-rights-coalition-nashville</t>
+  </si>
+  <si>
+    <t>Grant Analyst- Finance</t>
+  </si>
+  <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>USD 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19e3b77e3b1e4127b257c641713ded8a-grant-analyst-finance-jewish-association-serving-the-aging-new-york</t>
+  </si>
+  <si>
+    <t>Graphic Design &amp; Video Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc1044335b9f4544bcedcbc36db1a3a2-graphic-design-video-associate-cookies-for-kids-cancer-new-york</t>
+  </si>
+  <si>
+    <t>HCD Financial Analyst IV/Fund Analyst (C26022)</t>
+  </si>
+  <si>
+    <t>MD DHCD</t>
+  </si>
+  <si>
+    <t>Lanham, Maryland</t>
+  </si>
+  <si>
+    <t>USD 44.00 - 48.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/d5364c79980342ceab4c0e2569afd780-hcd-financial-analyst-ivfund-analyst-c26022-md-dhcd-lanham</t>
+  </si>
+  <si>
+    <t>Health Educator</t>
+  </si>
+  <si>
+    <t>Boston Public Health Commission</t>
+  </si>
+  <si>
+    <t>USD 835.29 - 993.46/week</t>
+  </si>
+  <si>
+    <t>Health Medicine, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43c9ebad527145b3b99b522a73786671-health-educator-boston-public-health-commission-boston</t>
+  </si>
+  <si>
+    <t>Housing Specialist (Manhattan)</t>
+  </si>
+  <si>
+    <t>Manhattan, NY</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Children Youth, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6fdfea078f144df91683b3131c54e1b-housing-specialist-manhattan-housing-solutions-of-new-york-manhattan</t>
+  </si>
+  <si>
+    <t>Housing Specialist (Queens)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5d9ee5cd12445a6b1b22965329db54d-housing-specialist-queens-housing-solutions-of-new-york-queens</t>
+  </si>
+  <si>
+    <t>Immigrants' Rights Managing Attorney</t>
+  </si>
+  <si>
+    <t>USD 111479.00 - 139332.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40b5a6429f99461f85b0d562fe81276b-immigrants-rights-managing-attorney-cair-san-francisco-bay-area-santa-clara</t>
+  </si>
+  <si>
+    <t>Individual Giving Coordinator</t>
+  </si>
+  <si>
+    <t>The Oakland Zoo</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>USD 28.68 - 30.73/hour</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/76d46c5554c14f66979144247febe7db-individual-giving-coordinator-the-oakland-zoo-oakland</t>
+  </si>
+  <si>
+    <t>Institutional Giving Manager</t>
+  </si>
+  <si>
+    <t>Tipping Point Community</t>
+  </si>
+  <si>
+    <t>USD 127836.00 - 127836.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6d2f988ce1648af99d0e6f393c9ea28-institutional-giving-manager-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
+    <t>Instructional Design Specialist</t>
+  </si>
+  <si>
+    <t>Constructive Dialogue Institute</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c3eef3b1ed04ed89440958da9ae0023-instructional-design-specialist-constructive-dialogue-institute-new-york</t>
+  </si>
+  <si>
+    <t>Intake Care Manager</t>
+  </si>
+  <si>
+    <t>Mystic Valley Elder Services</t>
+  </si>
+  <si>
+    <t>Malden, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 54566.15/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a27e46a82bcf48d68787e1511b2e84b6-intake-care-manager-mystic-valley-elder-services-malden</t>
+  </si>
+  <si>
+    <t>Labor Rights Organizer</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75b9c123be7746579eb598532e6196a5-labor-rights-organizer-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Lead Tenant Organizer and Civic Engagement Project Supervisor</t>
+  </si>
+  <si>
+    <t>Mass. Alliance of HUD Tenants</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/90c3d6a3f28a4eadb9c0861e8b05bcc7-lead-tenant-organizer-and-civic-engagement-project-supervisor-mass-alliance-of-hud-tenants-boston</t>
+  </si>
+  <si>
+    <t>Lead, Reviews (Early Math)</t>
+  </si>
+  <si>
+    <t>EdReports</t>
+  </si>
+  <si>
+    <t>USD 102000.00 - 139000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02e42e516ac14617b596896a3ee46703-lead-reviews-early-math-edreports-raleigh</t>
+  </si>
+  <si>
+    <t>Legal - Administrative Specialist</t>
+  </si>
+  <si>
+    <t>Crystal Stairs of Los Angeles</t>
+  </si>
+  <si>
+    <t>Ladera Heights, California</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef2a4ee254d54b789530da7962cdc4e4-legal-administrative-specialist-crystal-stairs-of-los-angeles-ladera-heights</t>
+  </si>
+  <si>
+    <t>Managing Editor</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75f70a52fc2e4fb18297876b9c692b4c-managing-editor-asian-arts-initiative-of-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Brand Manager</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/260bc58cf97c4c96b1ca21fea02d6f47-marketing-brand-manager-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Nursing Supervisor</t>
+  </si>
+  <si>
+    <t>Educational Alliance</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a1b0abc062e44d09e8f481c4c1401bd-nursing-supervisor-educational-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Red Caboose Child Care Center, Inc.</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 56160.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0debf47a058e404eb356f13930ce4359-operations-manager-red-caboose-child-care-center-inc-madison</t>
+  </si>
+  <si>
+    <t>Operations Manager (Bronx, Manhattan)</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc3798b52d734364acdb842c3023cfc9-operations-manager-bronx-manhattan-housing-solutions-of-new-york-manhattan</t>
+  </si>
+  <si>
+    <t>Philanthropic Giving Manager</t>
+  </si>
+  <si>
+    <t>Morgridge Institute for Research</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Health Medicine, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1623271c9bbf451cb71040b8bee66886-philanthropic-giving-manager-morgridge-institute-for-research-madison</t>
+  </si>
+  <si>
+    <t>Program &amp; Career Specialist</t>
+  </si>
+  <si>
+    <t>The Knowledge House</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0244b52838db45999901125875a2c313-program-career-specialist-the-knowledge-house-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/32249a0fd38546dbbfaab53e3d6fa8d3-program-coordinator-the-anbryce-foundation-washington</t>
+  </si>
+  <si>
     <t>Project Officer/Consultant</t>
   </si>
   <si>
@@ -49,16 +1552,331 @@
     <t>Remote (Kathmandu, Bagmati Province, NP)</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Lgbtq</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/dc4fa245e59642a69e94aa69ef944793-project-officerconsultant-women-welfare-foundation-kathmandu</t>
+  </si>
+  <si>
+    <t>Queens Regional Director, AG’s Intergovernmental Affairs (6461)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/b131ba3a476b4a098081b1185d1b00ab-queens-regional-director-ags-intergovernmental-affairs-6461-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Research + Innovation Director</t>
+  </si>
+  <si>
+    <t>USD 176872.00 - 176872.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ece8a3ad88446169423ffc45a8524a6-research-innovation-director-tipping-point-community-san-francisco</t>
+  </si>
+  <si>
+    <t>Research Supervisor Fellowship: Costa Rica</t>
+  </si>
+  <si>
+    <t>Canadian Organization for Tropical Education and Rainforest Conservation</t>
+  </si>
+  <si>
+    <t>Tortuguero, Limón Province, CR</t>
+  </si>
+  <si>
+    <t>USD 600.00 - 600.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8aa707def2614199b4dcf6e9504f7715-research-supervisor-fellowship-costa-rica-canadian-organization-for-tropical-education-and-rainforest-conservation-tortuguero</t>
+  </si>
+  <si>
+    <t>Residential Aide (Bronx)</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 17.50 - 18.46/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b2d5abfdb01467e9f3d4a5b0f7e315e-residential-aide-bronx-housing-solutions-of-new-york-bronx</t>
+  </si>
+  <si>
+    <t>Residential Aide (Brooklyn)</t>
+  </si>
+  <si>
+    <t>brooklyn, ny</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d815b874da64426a8faaf2b39e7336ae-residential-aide-brooklyn-housing-solutions-of-new-york-brooklyn</t>
+  </si>
+  <si>
+    <t>Residential Aide (Manhattan)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6054d526217e467e9ea62ea60d93144a-residential-aide-manhattan-housing-solutions-of-new-york-manhattan</t>
+  </si>
+  <si>
+    <t>Residential Aide (Queens)</t>
+  </si>
+  <si>
+    <t>queens, ny</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7bb9a17fb7b4db8920e5ec539370fcf-residential-aide-queens-housing-solutions-of-new-york-queens</t>
+  </si>
+  <si>
+    <t>Responsable Contable</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/284564f032a14f8e88897d9048537d89-responsable-contable-medicos-sin-fronteras-lat-buenos-aires</t>
+  </si>
+  <si>
+    <t>Retirement Business Analyst</t>
+  </si>
+  <si>
+    <t>USD 114754.00 - 127504.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/22f95b0018584db6a67a480dc54b0dd4-retirement-business-analyst-american-speech-language-hearing-association-rockville</t>
+  </si>
+  <si>
+    <t>Salesforce Administrator and Business Analyst</t>
+  </si>
+  <si>
+    <t>Wilshire Boulevard Temple</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e33384d1f8a4b26a4cba809234a51f8-salesforce-administrator-and-business-analyst-wilshire-boulevard-temple-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Association for Neighborhood and Housing Development</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 89000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fb2be2417424a3daf001e2226328971-senior-campaign-organizer-association-for-neighborhood-and-housing-development-new-york</t>
+  </si>
+  <si>
+    <t>Senior Director of Reentry Services</t>
+  </si>
+  <si>
+    <t>Jubilee Housing</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Civic Engagement, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/227a6f0e92004d948d5cdd72e0d80e3a-senior-director-of-reentry-services-jubilee-housing-washington</t>
+  </si>
+  <si>
+    <t>Senior Director, Individual Giving</t>
+  </si>
+  <si>
+    <t>SOME (So Others Might Eat)</t>
+  </si>
+  <si>
+    <t>USD 139318.00 - 147326.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6da0cf6b0af3412db6e2e9b8cbb21b70-senior-director-individual-giving-some-so-others-might-eat-washington</t>
+  </si>
+  <si>
+    <t>Senior Immigrants’ Rights Attorney</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/136673200fd7418cad08b602c2ea0959-senior-immigrants-rights-attorney-cair-san-francisco-bay-area-santa-clara</t>
+  </si>
+  <si>
+    <t>Senior Manager of Annual Giving &amp; Membership</t>
+  </si>
+  <si>
+    <t>Adirondack Mountain Club</t>
+  </si>
+  <si>
+    <t>Saratoga Springs, New York</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e23ad568ffb84945be12ad0730b504f2-senior-manager-of-annual-giving-membership-adirondack-mountain-club-saratoga-springs</t>
+  </si>
+  <si>
+    <t>Senior Manager of Finance &amp; Operations</t>
+  </si>
+  <si>
+    <t>Lighthouse Foundation of Chicagoland</t>
+  </si>
+  <si>
+    <t>Remote (Chicago, Illinois)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/687eb3de6c3b495aba73d1e9db09aa1d-senior-manager-of-finance-operations-lighthouse-foundation-of-chicagoland-chicago</t>
+  </si>
+  <si>
+    <t>Site Director (Queens)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Men</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0ffc9df25ac4efd998bc2f2a2d5d667-site-director-queens-housing-solutions-of-new-york-queens</t>
+  </si>
+  <si>
+    <t>Social Media Manager</t>
+  </si>
+  <si>
+    <t>651 ARTS</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f70b759f89024c248bbf8fa9c6f97ea8-social-media-manager-651-arts-kings-county</t>
+  </si>
+  <si>
+    <t>Special Events Assisant</t>
+  </si>
+  <si>
+    <t>Madison Square Boys &amp; Girls Club Foundation</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e36549fd59fa445e9c6e78551050b159-special-events-assisant-madison-square-boys-girls-club-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>exalt youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2655e9b1542a439f8c3f2164e58bb60f-staff-accountant-exalt-youth-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee8402856dc3495898ebae87ca74aa9d-staff-attorney-tennessee-immigrant-and-refugee-rights-coalition-nashville</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Direct Legal Services</t>
+  </si>
+  <si>
+    <t>The Human Trafficking Legal Center</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e295c800e1214bc0b109055e2e471241-staff-attorney-direct-legal-services-the-human-trafficking-legal-center-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Strategic Litigation</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/baa5fa51e1d64d70bb8164852e24b3e0-staff-attorney-strategic-litigation-the-human-trafficking-legal-center-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Victim Services</t>
+  </si>
+  <si>
+    <t>SeniorLAW Center</t>
+  </si>
+  <si>
+    <t>USD 66000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Human Rights Civil Liberties, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c23ff9cf7dd94eeba383e9e4c68b8e9f-staff-attorney-victim-services-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Synagogue Partnership Social Worker</t>
+  </si>
+  <si>
+    <t>DOROT</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/235b0a1b551d4ce698220e8a897e4c8f-synagogue-partnership-social-worker-dorot-new-york</t>
+  </si>
+  <si>
+    <t>Vice President of Advancement Operations</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/049705f31de04fb8a7ac10f01f5cb0b3-vice-president-of-advancement-operations-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Workforce Community Organizer</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67bf17abab1b4083a5011a98f6f8eff7-workforce-community-organizer-street-level-health-project-oakland</t>
   </si>
 </sst>
 </file>
@@ -444,7 +2262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -483,8 +2301,730 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" t="s">
+        <v>116</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F26" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" t="s">
+        <v>128</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -540,7 +3080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -581,31 +3121,2311 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="C2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" t="s">
+        <v>204</v>
+      </c>
+      <c r="F8" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F10" t="s">
+        <v>217</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" t="s">
+        <v>193</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" t="s">
+        <v>193</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" t="s">
+        <v>211</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" t="s">
+        <v>242</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" t="s">
+        <v>248</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>250</v>
+      </c>
+      <c r="B17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" t="s">
+        <v>252</v>
+      </c>
+      <c r="F17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B18" t="s">
+        <v>256</v>
+      </c>
+      <c r="C18" t="s">
+        <v>257</v>
+      </c>
+      <c r="D18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" t="s">
+        <v>258</v>
+      </c>
+      <c r="F18" t="s">
+        <v>259</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" t="s">
+        <v>265</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F20" t="s">
+        <v>271</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" t="s">
+        <v>276</v>
+      </c>
+      <c r="F21" t="s">
+        <v>277</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" t="s">
+        <v>283</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" t="s">
+        <v>286</v>
+      </c>
+      <c r="C23" t="s">
+        <v>287</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F23" t="s">
+        <v>289</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" t="s">
+        <v>293</v>
+      </c>
+      <c r="E24" t="s">
+        <v>294</v>
+      </c>
+      <c r="F24" t="s">
+        <v>295</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" t="s">
+        <v>298</v>
+      </c>
+      <c r="D25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E25" t="s">
+        <v>299</v>
+      </c>
+      <c r="F25" t="s">
+        <v>295</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>301</v>
+      </c>
+      <c r="B26" t="s">
+        <v>302</v>
+      </c>
+      <c r="C26" t="s">
+        <v>303</v>
+      </c>
+      <c r="D26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" t="s">
+        <v>305</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>307</v>
+      </c>
+      <c r="B27" t="s">
+        <v>308</v>
+      </c>
+      <c r="C27" t="s">
+        <v>309</v>
+      </c>
+      <c r="D27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" t="s">
+        <v>310</v>
+      </c>
+      <c r="F27" t="s">
+        <v>311</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B28" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" t="s">
+        <v>225</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>315</v>
+      </c>
+      <c r="F28" t="s">
+        <v>316</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29" t="s">
+        <v>319</v>
+      </c>
+      <c r="C29" t="s">
+        <v>309</v>
+      </c>
+      <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
+        <v>320</v>
+      </c>
+      <c r="F29" t="s">
+        <v>321</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>323</v>
+      </c>
+      <c r="B30" t="s">
+        <v>324</v>
+      </c>
+      <c r="C30" t="s">
+        <v>325</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>326</v>
+      </c>
+      <c r="F30" t="s">
+        <v>327</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>329</v>
+      </c>
+      <c r="B31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C31" t="s">
+        <v>331</v>
+      </c>
+      <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>332</v>
+      </c>
+      <c r="F31" t="s">
+        <v>333</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>329</v>
+      </c>
+      <c r="B32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C32" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>335</v>
+      </c>
+      <c r="F32" t="s">
+        <v>336</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>338</v>
+      </c>
+      <c r="B33" t="s">
+        <v>339</v>
+      </c>
+      <c r="C33" t="s">
+        <v>340</v>
+      </c>
+      <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
+        <v>341</v>
+      </c>
+      <c r="F33" t="s">
+        <v>342</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>344</v>
+      </c>
+      <c r="B34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C34" t="s">
+        <v>346</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>347</v>
+      </c>
+      <c r="F34" t="s">
+        <v>348</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B35" t="s">
+        <v>351</v>
+      </c>
+      <c r="C35" t="s">
+        <v>352</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>353</v>
+      </c>
+      <c r="F35" t="s">
+        <v>354</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>356</v>
+      </c>
+      <c r="B36" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" t="s">
+        <v>358</v>
+      </c>
+      <c r="E36" t="s">
+        <v>359</v>
+      </c>
+      <c r="F36" t="s">
+        <v>360</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>362</v>
+      </c>
+      <c r="B37" t="s">
+        <v>363</v>
+      </c>
+      <c r="C37" t="s">
+        <v>309</v>
+      </c>
+      <c r="D37" t="s">
+        <v>293</v>
+      </c>
+      <c r="E37" t="s">
+        <v>364</v>
+      </c>
+      <c r="F37" t="s">
+        <v>365</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>367</v>
+      </c>
+      <c r="B38" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" t="s">
+        <v>369</v>
+      </c>
+      <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>370</v>
+      </c>
+      <c r="F38" t="s">
+        <v>371</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>373</v>
+      </c>
+      <c r="B39" t="s">
+        <v>374</v>
+      </c>
+      <c r="C39" t="s">
+        <v>375</v>
+      </c>
+      <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>376</v>
+      </c>
+      <c r="F39" t="s">
+        <v>295</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" t="s">
+        <v>378</v>
+      </c>
+      <c r="C40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>379</v>
+      </c>
+      <c r="F40" t="s">
+        <v>289</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" t="s">
+        <v>381</v>
+      </c>
+      <c r="C41" t="s">
+        <v>382</v>
+      </c>
+      <c r="D41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
+        <v>383</v>
+      </c>
+      <c r="F41" t="s">
+        <v>321</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>385</v>
+      </c>
+      <c r="B42" t="s">
+        <v>386</v>
+      </c>
+      <c r="C42" t="s">
+        <v>309</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>387</v>
+      </c>
+      <c r="F42" t="s">
+        <v>388</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>390</v>
+      </c>
+      <c r="B43" t="s">
+        <v>391</v>
+      </c>
+      <c r="C43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" t="s">
+        <v>392</v>
+      </c>
+      <c r="E43" t="s">
+        <v>393</v>
+      </c>
+      <c r="F43" t="s">
+        <v>388</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>395</v>
+      </c>
+      <c r="B44" t="s">
+        <v>396</v>
+      </c>
+      <c r="C44" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
+      <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" t="s">
+        <v>397</v>
+      </c>
+      <c r="F44" t="s">
+        <v>398</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>400</v>
+      </c>
+      <c r="B45" t="s">
+        <v>401</v>
+      </c>
+      <c r="C45" t="s">
+        <v>402</v>
+      </c>
+      <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>403</v>
+      </c>
+      <c r="F45" t="s">
+        <v>259</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>405</v>
+      </c>
+      <c r="B46" t="s">
+        <v>401</v>
+      </c>
+      <c r="C46" t="s">
+        <v>402</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>406</v>
+      </c>
+      <c r="F46" t="s">
+        <v>259</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>408</v>
+      </c>
+      <c r="B47" t="s">
+        <v>409</v>
+      </c>
+      <c r="C47" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s">
+        <v>410</v>
+      </c>
+      <c r="F47" t="s">
+        <v>193</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>412</v>
+      </c>
+      <c r="B48" t="s">
+        <v>308</v>
+      </c>
+      <c r="C48" t="s">
+        <v>309</v>
+      </c>
+      <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" t="s">
+        <v>204</v>
+      </c>
+      <c r="F48" t="s">
+        <v>311</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>414</v>
+      </c>
+      <c r="B49" t="s">
+        <v>415</v>
+      </c>
+      <c r="C49" t="s">
+        <v>416</v>
+      </c>
+      <c r="D49" t="s">
+        <v>392</v>
+      </c>
+      <c r="E49" t="s">
+        <v>417</v>
+      </c>
+      <c r="F49" t="s">
+        <v>418</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>420</v>
+      </c>
+      <c r="B50" t="s">
+        <v>421</v>
+      </c>
+      <c r="C50" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" t="s">
+        <v>422</v>
+      </c>
+      <c r="F50" t="s">
+        <v>423</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>425</v>
+      </c>
+      <c r="B51" t="s">
+        <v>345</v>
+      </c>
+      <c r="C51" t="s">
+        <v>426</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>427</v>
+      </c>
+      <c r="F51" t="s">
+        <v>428</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>430</v>
+      </c>
+      <c r="B52" t="s">
+        <v>345</v>
+      </c>
+      <c r="C52" t="s">
+        <v>346</v>
+      </c>
+      <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>427</v>
+      </c>
+      <c r="F52" t="s">
+        <v>428</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>432</v>
+      </c>
+      <c r="B53" t="s">
+        <v>256</v>
+      </c>
+      <c r="C53" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" t="s">
+        <v>433</v>
+      </c>
+      <c r="F53" t="s">
+        <v>259</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>435</v>
+      </c>
+      <c r="B54" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54" t="s">
+        <v>437</v>
+      </c>
+      <c r="D54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" t="s">
+        <v>438</v>
+      </c>
+      <c r="F54" t="s">
+        <v>439</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>441</v>
+      </c>
+      <c r="B55" t="s">
+        <v>442</v>
+      </c>
+      <c r="C55" t="s">
+        <v>352</v>
+      </c>
+      <c r="D55" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>443</v>
+      </c>
+      <c r="F55" t="s">
+        <v>444</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>446</v>
+      </c>
+      <c r="B56" t="s">
+        <v>447</v>
+      </c>
+      <c r="C56" t="s">
+        <v>309</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" t="s">
+        <v>448</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>450</v>
+      </c>
+      <c r="B57" t="s">
+        <v>451</v>
+      </c>
+      <c r="C57" t="s">
+        <v>452</v>
+      </c>
+      <c r="D57" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" t="s">
+        <v>453</v>
+      </c>
+      <c r="F57" t="s">
+        <v>193</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>455</v>
+      </c>
+      <c r="B58" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58" t="s">
+        <v>281</v>
+      </c>
+      <c r="D58" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" t="s">
+        <v>456</v>
+      </c>
+      <c r="F58" t="s">
+        <v>283</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>458</v>
+      </c>
+      <c r="B59" t="s">
+        <v>459</v>
+      </c>
+      <c r="C59" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" t="s">
+        <v>460</v>
+      </c>
+      <c r="F59" t="s">
+        <v>461</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>463</v>
+      </c>
+      <c r="B60" t="s">
+        <v>464</v>
+      </c>
+      <c r="C60" t="s">
+        <v>309</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
+        <v>465</v>
+      </c>
+      <c r="F60" t="s">
+        <v>211</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>467</v>
+      </c>
+      <c r="B61" t="s">
+        <v>468</v>
+      </c>
+      <c r="C61" t="s">
+        <v>469</v>
+      </c>
+      <c r="D61" t="s">
+        <v>173</v>
+      </c>
+      <c r="E61" t="s">
+        <v>470</v>
+      </c>
+      <c r="F61" t="s">
+        <v>471</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>473</v>
+      </c>
+      <c r="B62" t="s">
+        <v>286</v>
+      </c>
+      <c r="C62" t="s">
+        <v>287</v>
+      </c>
+      <c r="D62" t="s">
+        <v>230</v>
+      </c>
+      <c r="E62" t="s">
+        <v>474</v>
+      </c>
+      <c r="F62" t="s">
+        <v>289</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>476</v>
+      </c>
+      <c r="B63" t="s">
+        <v>477</v>
+      </c>
+      <c r="C63" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
+        <v>478</v>
+      </c>
+      <c r="F63" t="s">
+        <v>479</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>481</v>
+      </c>
+      <c r="B64" t="s">
+        <v>482</v>
+      </c>
+      <c r="C64" t="s">
+        <v>225</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" t="s">
+        <v>276</v>
+      </c>
+      <c r="F64" t="s">
+        <v>483</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>485</v>
+      </c>
+      <c r="B65" t="s">
+        <v>486</v>
+      </c>
+      <c r="C65" t="s">
+        <v>487</v>
+      </c>
+      <c r="D65" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" t="s">
+        <v>488</v>
+      </c>
+      <c r="F65" t="s">
+        <v>489</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>491</v>
+      </c>
+      <c r="B66" t="s">
+        <v>345</v>
+      </c>
+      <c r="C66" t="s">
+        <v>426</v>
+      </c>
+      <c r="D66" t="s">
+        <v>173</v>
+      </c>
+      <c r="E66" t="s">
+        <v>492</v>
+      </c>
+      <c r="F66" t="s">
+        <v>493</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>495</v>
+      </c>
+      <c r="B67" t="s">
+        <v>496</v>
+      </c>
+      <c r="C67" t="s">
+        <v>487</v>
+      </c>
+      <c r="D67" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" t="s">
+        <v>497</v>
+      </c>
+      <c r="F67" t="s">
+        <v>498</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>500</v>
+      </c>
+      <c r="B68" t="s">
+        <v>501</v>
+      </c>
+      <c r="C68" t="s">
+        <v>225</v>
+      </c>
+      <c r="D68" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" t="s">
+        <v>502</v>
+      </c>
+      <c r="F68" t="s">
+        <v>503</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>505</v>
+      </c>
+      <c r="B69" t="s">
+        <v>196</v>
+      </c>
+      <c r="C69" t="s">
+        <v>197</v>
+      </c>
+      <c r="D69" t="s">
+        <v>173</v>
+      </c>
+      <c r="E69" t="s">
+        <v>506</v>
+      </c>
+      <c r="F69" t="s">
+        <v>507</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>509</v>
+      </c>
+      <c r="B70" t="s">
+        <v>510</v>
+      </c>
+      <c r="C70" t="s">
+        <v>511</v>
+      </c>
+      <c r="D70" t="s">
+        <v>392</v>
+      </c>
+      <c r="E70" t="s">
+        <v>193</v>
+      </c>
+      <c r="F70" t="s">
+        <v>512</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>514</v>
+      </c>
+      <c r="B71" t="s">
+        <v>224</v>
+      </c>
+      <c r="C71" t="s">
+        <v>225</v>
+      </c>
+      <c r="D71" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" t="s">
+        <v>226</v>
+      </c>
+      <c r="F71" t="s">
+        <v>193</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>516</v>
+      </c>
+      <c r="B72" t="s">
+        <v>442</v>
+      </c>
+      <c r="C72" t="s">
+        <v>352</v>
+      </c>
+      <c r="D72" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" t="s">
+        <v>517</v>
+      </c>
+      <c r="F72" t="s">
+        <v>444</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>519</v>
+      </c>
+      <c r="B73" t="s">
+        <v>520</v>
+      </c>
+      <c r="C73" t="s">
+        <v>521</v>
+      </c>
+      <c r="D73" t="s">
+        <v>358</v>
+      </c>
+      <c r="E73" t="s">
+        <v>522</v>
+      </c>
+      <c r="F73" t="s">
+        <v>360</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>524</v>
+      </c>
+      <c r="B74" t="s">
+        <v>345</v>
+      </c>
+      <c r="C74" t="s">
+        <v>525</v>
+      </c>
+      <c r="D74" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" t="s">
+        <v>526</v>
+      </c>
+      <c r="F74" t="s">
+        <v>527</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>529</v>
+      </c>
+      <c r="B75" t="s">
+        <v>345</v>
+      </c>
+      <c r="C75" t="s">
+        <v>530</v>
+      </c>
+      <c r="D75" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" t="s">
+        <v>526</v>
+      </c>
+      <c r="F75" t="s">
+        <v>527</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>532</v>
+      </c>
+      <c r="B76" t="s">
+        <v>345</v>
+      </c>
+      <c r="C76" t="s">
+        <v>426</v>
+      </c>
+      <c r="D76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" t="s">
+        <v>526</v>
+      </c>
+      <c r="F76" t="s">
+        <v>527</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>534</v>
+      </c>
+      <c r="B77" t="s">
+        <v>345</v>
+      </c>
+      <c r="C77" t="s">
+        <v>535</v>
+      </c>
+      <c r="D77" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" t="s">
+        <v>526</v>
+      </c>
+      <c r="F77" t="s">
+        <v>527</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>537</v>
+      </c>
+      <c r="B78" t="s">
+        <v>538</v>
+      </c>
+      <c r="C78" t="s">
+        <v>539</v>
+      </c>
+      <c r="D78" t="s">
+        <v>173</v>
+      </c>
+      <c r="E78" t="s">
+        <v>193</v>
+      </c>
+      <c r="F78" t="s">
+        <v>540</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>542</v>
+      </c>
+      <c r="B79" t="s">
+        <v>268</v>
+      </c>
+      <c r="C79" t="s">
+        <v>269</v>
+      </c>
+      <c r="D79" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" t="s">
+        <v>543</v>
+      </c>
+      <c r="F79" t="s">
+        <v>271</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>545</v>
+      </c>
+      <c r="B80" t="s">
+        <v>546</v>
+      </c>
+      <c r="C80" t="s">
+        <v>309</v>
+      </c>
+      <c r="D80" t="s">
+        <v>173</v>
+      </c>
+      <c r="E80" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" t="s">
+        <v>371</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>548</v>
+      </c>
+      <c r="B81" t="s">
+        <v>549</v>
+      </c>
+      <c r="C81" t="s">
+        <v>225</v>
+      </c>
+      <c r="D81" t="s">
+        <v>173</v>
+      </c>
+      <c r="E81" t="s">
+        <v>550</v>
+      </c>
+      <c r="F81" t="s">
+        <v>551</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>553</v>
+      </c>
+      <c r="B82" t="s">
+        <v>554</v>
+      </c>
+      <c r="C82" t="s">
+        <v>197</v>
+      </c>
+      <c r="D82" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" t="s">
+        <v>555</v>
+      </c>
+      <c r="F82" t="s">
+        <v>556</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>558</v>
+      </c>
+      <c r="B83" t="s">
+        <v>559</v>
+      </c>
+      <c r="C83" t="s">
+        <v>197</v>
+      </c>
+      <c r="D83" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" t="s">
+        <v>560</v>
+      </c>
+      <c r="F83" t="s">
+        <v>561</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>563</v>
+      </c>
+      <c r="B84" t="s">
+        <v>256</v>
+      </c>
+      <c r="C84" t="s">
+        <v>257</v>
+      </c>
+      <c r="D84" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" t="s">
+        <v>564</v>
+      </c>
+      <c r="F84" t="s">
+        <v>259</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>566</v>
+      </c>
+      <c r="B85" t="s">
+        <v>567</v>
+      </c>
+      <c r="C85" t="s">
+        <v>568</v>
+      </c>
+      <c r="D85" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" t="s">
+        <v>569</v>
+      </c>
+      <c r="F85" t="s">
+        <v>570</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>572</v>
+      </c>
+      <c r="B86" t="s">
+        <v>573</v>
+      </c>
+      <c r="C86" t="s">
+        <v>574</v>
+      </c>
+      <c r="D86" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" t="s">
+        <v>575</v>
+      </c>
+      <c r="F86" t="s">
+        <v>576</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>578</v>
+      </c>
+      <c r="B87" t="s">
+        <v>345</v>
+      </c>
+      <c r="C87" t="s">
+        <v>346</v>
+      </c>
+      <c r="D87" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" t="s">
+        <v>579</v>
+      </c>
+      <c r="F87" t="s">
+        <v>580</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>582</v>
+      </c>
+      <c r="B88" t="s">
+        <v>583</v>
+      </c>
+      <c r="C88" t="s">
+        <v>584</v>
+      </c>
+      <c r="D88" t="s">
+        <v>293</v>
+      </c>
+      <c r="E88" t="s">
+        <v>585</v>
+      </c>
+      <c r="F88" t="s">
+        <v>586</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>588</v>
+      </c>
+      <c r="B89" t="s">
+        <v>589</v>
+      </c>
+      <c r="C89" t="s">
+        <v>225</v>
+      </c>
+      <c r="D89" t="s">
+        <v>173</v>
+      </c>
+      <c r="E89" t="s">
+        <v>590</v>
+      </c>
+      <c r="F89" t="s">
+        <v>591</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>593</v>
+      </c>
+      <c r="B90" t="s">
+        <v>594</v>
+      </c>
+      <c r="C90" t="s">
+        <v>225</v>
+      </c>
+      <c r="D90" t="s">
+        <v>173</v>
+      </c>
+      <c r="E90" t="s">
+        <v>478</v>
+      </c>
+      <c r="F90" t="s">
+        <v>489</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>596</v>
+      </c>
+      <c r="B91" t="s">
+        <v>401</v>
+      </c>
+      <c r="C91" t="s">
+        <v>402</v>
+      </c>
+      <c r="D91" t="s">
+        <v>173</v>
+      </c>
+      <c r="E91" t="s">
+        <v>347</v>
+      </c>
+      <c r="F91" t="s">
+        <v>259</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>598</v>
+      </c>
+      <c r="B92" t="s">
+        <v>599</v>
+      </c>
+      <c r="C92" t="s">
+        <v>197</v>
+      </c>
+      <c r="D92" t="s">
+        <v>173</v>
+      </c>
+      <c r="E92" t="s">
+        <v>198</v>
+      </c>
+      <c r="F92" t="s">
+        <v>600</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>602</v>
+      </c>
+      <c r="B93" t="s">
+        <v>599</v>
+      </c>
+      <c r="C93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D93" t="s">
+        <v>173</v>
+      </c>
+      <c r="E93" t="s">
+        <v>198</v>
+      </c>
+      <c r="F93" t="s">
+        <v>603</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>605</v>
+      </c>
+      <c r="B94" t="s">
+        <v>606</v>
+      </c>
+      <c r="C94" t="s">
+        <v>287</v>
+      </c>
+      <c r="D94" t="s">
+        <v>173</v>
+      </c>
+      <c r="E94" t="s">
+        <v>607</v>
+      </c>
+      <c r="F94" t="s">
+        <v>608</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>610</v>
+      </c>
+      <c r="B95" t="s">
+        <v>611</v>
+      </c>
+      <c r="C95" t="s">
+        <v>225</v>
+      </c>
+      <c r="D95" t="s">
+        <v>173</v>
+      </c>
+      <c r="E95" t="s">
+        <v>612</v>
+      </c>
+      <c r="F95" t="s">
+        <v>613</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>615</v>
+      </c>
+      <c r="B96" t="s">
+        <v>616</v>
+      </c>
+      <c r="C96" t="s">
+        <v>298</v>
+      </c>
+      <c r="D96" t="s">
+        <v>173</v>
+      </c>
+      <c r="E96" t="s">
+        <v>617</v>
+      </c>
+      <c r="F96" t="s">
+        <v>193</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>619</v>
+      </c>
+      <c r="B97" t="s">
+        <v>280</v>
+      </c>
+      <c r="C97" t="s">
+        <v>281</v>
+      </c>
+      <c r="D97" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" t="s">
+        <v>456</v>
+      </c>
+      <c r="F97" t="s">
+        <v>283</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/xlsx/jobs-2026-09-30.xlsx
+++ b/docs/xlsx/jobs-2026-09-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="788">
   <si>
     <t>Title</t>
   </si>
@@ -673,6 +673,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/243787d2142141bd8f07c756c4782a55-associate-director-education-policy-cea-flexible-within-the-us-south-or-midwest-preferred-ajc-new-york</t>
   </si>
   <si>
+    <t>Associate I, Evidence for Outcomes</t>
+  </si>
+  <si>
+    <t>Project Evident</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87f84632a62943b99ab19b591f1c67f6-associate-i-evidence-for-outcomes-project-evident-boston</t>
+  </si>
+  <si>
     <t>ATTAIN Lab Coordinator, NYC - Staten Island</t>
   </si>
   <si>
@@ -685,6 +700,18 @@
     <t>https://www.idealist.org/en/job/76dd1d5e018c4e528793444c3d927f50-attain-lab-coordinator-nyc-staten-island-the-research-foundation-for-suny-staten-island</t>
   </si>
   <si>
+    <t>Audiovisual (AV) Specialist</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7dde72cffe9946f7a285c6c7757d6380-audiovisual-av-specialist-meridian-international-center-washington</t>
+  </si>
+  <si>
     <t>Brooklyn Regional Director, AG’s Intergovernmental Affairs (6462)</t>
   </si>
   <si>
@@ -748,6 +775,24 @@
     <t>https://www.idealist.org/en/job/ba68ff719c254f50bf30d5ebb9af6170-chief-financial-and-administrative-officer-the-clean-slate-initiative-orlando</t>
   </si>
   <si>
+    <t>Chief Program and Strategy Officer</t>
+  </si>
+  <si>
+    <t>ACLU of Idaho</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7df9e8f68c04e28a7d05c99f86534cd-chief-program-and-strategy-officer-aclu-of-idaho-boise</t>
+  </si>
+  <si>
     <t>Coastal Reporter-Producer</t>
   </si>
   <si>
@@ -817,6 +862,27 @@
     <t>https://www.idealist.org/en/business-job/8a0a36010b6644e485dd8b593e96ef35-community-outreach-rep-sustainability-nutrition-portland-full-circle-portland</t>
   </si>
   <si>
+    <t>Controller (Contract Position)</t>
+  </si>
+  <si>
+    <t>Bethany Baptist Church</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 80.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eeaadd7d7dbe4741b3519ca6263c9c4f-controller-contract-position-bethany-baptist-church-newark</t>
+  </si>
+  <si>
     <t>Coordinator, CE Provider Approval</t>
   </si>
   <si>
@@ -871,6 +937,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/5c52002d54e2441da51b5af34b625d7e-day-labor-lead-organizer-street-level-health-project-oakland</t>
   </si>
   <si>
+    <t>Dean, NYU School of Law</t>
+  </si>
+  <si>
+    <t>New York University School of Law</t>
+  </si>
+  <si>
+    <t>USD 644000.00 - 714000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ac1ea30065b42c196f23b948615e451-dean-nyu-school-of-law-new-york-university-school-of-law-new-york</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Irish Arts Center</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d37ce5d7a6e4a4f91b4d50038973aca-development-associate-irish-arts-center-new-york</t>
+  </si>
+  <si>
+    <t>Cabrillo Festival of Contemporary Music</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e6f2f5108744e1c9c82681257af1eb9-development-associate-cabrillo-festival-of-contemporary-music-santa-cruz</t>
+  </si>
+  <si>
     <t>Development Coordinator</t>
   </si>
   <si>
@@ -895,9 +1000,6 @@
     <t>The Cathedral Church of Saint John the Divine of New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 38.00 - 42.00/hour</t>
   </si>
   <si>
@@ -1048,6 +1150,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce90a7b47f8d4152b183bb0cc322959e-director-of-finance-and-operations-leap-for-education-inc-salem</t>
   </si>
   <si>
+    <t>Director of Operations and Facilities</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b4b094970434daba9d17e0a41c3017b-director-of-operations-and-facilities-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Director of Social Services (Queens)</t>
   </si>
   <si>
@@ -1084,6 +1204,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c9a0ee6f2c054174a97e7a4aed28af89-director-of-strategic-philanthropy-hamilton-families-san-francisco</t>
   </si>
   <si>
+    <t>Director, Cures Collective</t>
+  </si>
+  <si>
+    <t>I AM ALS</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffaa581e60cc46359ca43c10bac10983-director-cures-collective-i-am-als-washington</t>
+  </si>
+  <si>
     <t>Environmental Educator</t>
   </si>
   <si>
@@ -1102,6 +1237,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b7fa71c20e654c24adedc28319be5346-environmental-educator-christodora-nature-learning-leadership-new-york</t>
   </si>
   <si>
+    <t>Events Associate or Manager</t>
+  </si>
+  <si>
+    <t>National Immigration Project</t>
+  </si>
+  <si>
+    <t>USD 68850.00 - 76680.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f213bffd8f71402796266dc417a8ea00-events-associate-or-manager-national-immigration-project-washington</t>
+  </si>
+  <si>
     <t>Executive Assistant</t>
   </si>
   <si>
@@ -1129,9 +1279,6 @@
     <t>USD 70000.00 - 85000.00/year</t>
   </si>
   <si>
-    <t>Religion Spirituality</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/ec60ddbb07cf4a1e80b74f4ef1706685-executive-assistant-to-the-senior-pastorhead-of-staff-fourth-presbyterian-church-of-chicago-chicago</t>
   </si>
   <si>
@@ -1171,6 +1318,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/f52734dd63e64c65acf4524898c2c2d6-executive-director-william-a-harrison-jr-foundation-richmond</t>
   </si>
   <si>
+    <t>Tilth Alliance</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/037e3f5167b64f99bbeb44429b82d5c6-executive-director-tilth-alliance-seattle</t>
+  </si>
+  <si>
+    <t>Executive Director - Animal Protection Society of Durham</t>
+  </si>
+  <si>
+    <t>Armstrong McGuire &amp; Associates</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/b7ed69a6ffb04f059d46f4b8a988ad39-executive-director-animal-protection-society-of-durham-armstrong-mcguire-associates-durham</t>
+  </si>
+  <si>
     <t>Executive Director / Head of U.S. Operations - Friends of The Buddha Fellows</t>
   </si>
   <si>
@@ -1186,15 +1363,30 @@
     <t>https://www.idealist.org/en/business-job/d194fa5ca99346978900fd3cdd0b69c8-executive-director-head-of-us-operations-friends-of-the-buddha-fellows-equal-innovation-boston</t>
   </si>
   <si>
+    <t>Executive Director, Ignite! Utah Action</t>
+  </si>
+  <si>
+    <t>Ignite! Utah Action</t>
+  </si>
+  <si>
+    <t>Salt Lake City, Utah</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/40706a29ba244b9d9040483384ae6669-executive-director-ignite-utah-action-ignite-utah-action-salt-lake-city</t>
+  </si>
+  <si>
     <t>Facilitator</t>
   </si>
   <si>
     <t>National Cares Mentoring Movement</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 0.00 - 70.00/hour</t>
   </si>
   <si>
@@ -1312,6 +1504,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c5d9ee5cd12445a6b1b22965329db54d-housing-specialist-queens-housing-solutions-of-new-york-queens</t>
   </si>
   <si>
+    <t>HUD Tenant Rights Counselor</t>
+  </si>
+  <si>
+    <t>Housing Rights Committee of San Francisco</t>
+  </si>
+  <si>
+    <t>USD 36.54 - 36.54/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/65a841ac60424812b893b04c2ec2912d-hud-tenant-rights-counselor-housing-rights-committee-of-san-francisco-san-francisco</t>
+  </si>
+  <si>
     <t>Immigrants' Rights Managing Attorney</t>
   </si>
   <si>
@@ -1381,6 +1588,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a27e46a82bcf48d68787e1511b2e84b6-intake-care-manager-mystic-valley-elder-services-malden</t>
   </si>
   <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1acb52ce0a454a03ab20f1bffa19884e-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
     <t>Labor Rights Organizer</t>
   </si>
   <si>
@@ -1435,6 +1657,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/ef2a4ee254d54b789530da7962cdc4e4-legal-administrative-specialist-crystal-stairs-of-los-angeles-ladera-heights</t>
   </si>
   <si>
+    <t>Líder de proyecto para plataforma educativa y uso de redes sociales</t>
+  </si>
+  <si>
+    <t>Impacto Digital</t>
+  </si>
+  <si>
+    <t>Ciudad Autónoma de Buenos Aires, CABA, AR</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Science Technology, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c76413c549d49e9ac355988ab4282f8-lider-de-proyecto-para-plataforma-educativa-y-uso-de-redes-sociales-impacto-digital-ciudad-autonoma-de-buenos-aires</t>
+  </si>
+  <si>
+    <t>Life Saving Team Assistant</t>
+  </si>
+  <si>
+    <t>Kitty Bungalow Charm School for Wayward Cats</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c82abfe032b4b72a655ff7ac4522fa7-life-saving-team-assistant-kitty-bungalow-charm-school-for-wayward-cats-los-angeles</t>
+  </si>
+  <si>
+    <t>Loan Officer</t>
+  </si>
+  <si>
+    <t>United Counties EDC</t>
+  </si>
+  <si>
+    <t>Cranford, NJ</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/715c2587b34048de883f3d61f8279300-loan-officer-united-counties-edc-cranford</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer, Family Philanthropy</t>
+  </si>
+  <si>
+    <t>The Marine Mammal Center</t>
+  </si>
+  <si>
+    <t>Sausalito, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7539f4b11e84cc5803589d3b13f63da-major-gifts-officer-family-philanthropy-the-marine-mammal-center-sausalito</t>
+  </si>
+  <si>
     <t>Managing Editor</t>
   </si>
   <si>
@@ -1459,6 +1747,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/260bc58cf97c4c96b1ca21fea02d6f47-marketing-brand-manager-young-peoples-chorus-of-nyc-new-york</t>
   </si>
   <si>
+    <t>Marketing and Operations Manager</t>
+  </si>
+  <si>
+    <t>American Council of Learned Societies</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5bb069c373f47d0a8aaa27f949f2e5b-marketing-and-operations-manager-american-council-of-learned-societies-new-york</t>
+  </si>
+  <si>
+    <t>Media Relations and Content Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e1dcd2aac244baa8ca66ff8f9323927-media-relations-and-content-manager-american-council-of-learned-societies-new-york</t>
+  </si>
+  <si>
     <t>Nursing Supervisor</t>
   </si>
   <si>
@@ -1471,6 +1780,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a1b0abc062e44d09e8f481c4c1401bd-nursing-supervisor-educational-alliance-new-york</t>
   </si>
   <si>
+    <t>Operations and Finance Coordinator</t>
+  </si>
+  <si>
+    <t>Equity Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 30000.00 - 30000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4eac7f1ae1004c66a0da670136c2adfe-operations-and-finance-coordinator-equity-legal-services-inc-belleville</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -1492,9 +1819,6 @@
     <t>Operations Manager (Bronx, Manhattan)</t>
   </si>
   <si>
-    <t>USD 70000.00 - 70000.00/year</t>
-  </si>
-  <si>
     <t>Housing Homelessness, Mental Health, Substance Abuse Addiction</t>
   </si>
   <si>
@@ -1516,6 +1840,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/1623271c9bbf451cb71040b8bee66886-philanthropic-giving-manager-morgridge-institute-for-research-madison</t>
   </si>
   <si>
+    <t>President &amp; Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>One Hundred Miles</t>
+  </si>
+  <si>
+    <t>Brunswick, Georgia</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/552b4f9e90624449b3b99167bf6a0a06-president-chief-executive-officer-one-hundred-miles-brunswick</t>
+  </si>
+  <si>
+    <t>President and CEO</t>
+  </si>
+  <si>
+    <t>Project R.E.S.T.</t>
+  </si>
+  <si>
+    <t>Spartanburg, South Carolina</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d64ff8564a1a4a1390f7e1a5d7cbd706-president-and-ceo-project-rest-spartanburg</t>
+  </si>
+  <si>
     <t>Program &amp; Career Specialist</t>
   </si>
   <si>
@@ -1531,6 +1888,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0244b52838db45999901125875a2c313-program-career-specialist-the-knowledge-house-new-york</t>
   </si>
   <si>
+    <t>Program Associate of Community Bridges</t>
+  </si>
+  <si>
+    <t>Safe &amp; Sound</t>
+  </si>
+  <si>
+    <t>USD 36.46 - 36.46/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8db0de12e1ad464a9473976c73b0e4ec-program-associate-of-community-bridges-safe-sound-san-francisco</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -1543,6 +1915,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/32249a0fd38546dbbfaab53e3d6fa8d3-program-coordinator-the-anbryce-foundation-washington</t>
   </si>
   <si>
+    <t>Program Manager, Training Solutions</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8800950b578f4e0a8e31ee4a48ff8b1e-program-manager-training-solutions-the-knowledge-house-new-york</t>
+  </si>
+  <si>
+    <t>Program Support Associate – Center for Transformational Leadership</t>
+  </si>
+  <si>
+    <t>Southern New England Conference, United Church of Christ</t>
+  </si>
+  <si>
+    <t>Framingham, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 24.96 - 24.96/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/665bd148555a4cd399e52f4559f7d173-program-support-associate-center-for-transformational-leadership-southern-new-england-conference-united-church-of-christ-framingham</t>
+  </si>
+  <si>
     <t>Project Officer/Consultant</t>
   </si>
   <si>
@@ -1660,6 +2056,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/0e33384d1f8a4b26a4cba809234a51f8-salesforce-administrator-and-business-analyst-wilshire-boulevard-temple-los-angeles</t>
   </si>
   <si>
+    <t>Senior Accounting Associate, Foundation and Community</t>
+  </si>
+  <si>
+    <t>Steven &amp; Alexandra Cohen Foundation</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23995a05816f48c0b6a25ae4caa3c958-senior-accounting-associate-foundation-and-community-steven-alexandra-cohen-foundation-stamford</t>
+  </si>
+  <si>
     <t>Senior Campaign Organizer</t>
   </si>
   <si>
@@ -1750,6 +2161,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/687eb3de6c3b495aba73d1e9db09aa1d-senior-manager-of-finance-operations-lighthouse-foundation-of-chicagoland-chicago</t>
   </si>
   <si>
+    <t>Senior Program Manager - Community Partnerships</t>
+  </si>
+  <si>
+    <t>USD 91154.00 - 91154.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ebeaf36c0f144f9a9e0d1014dd2df6f7-senior-program-manager-community-partnerships-safe-sound-san-francisco</t>
+  </si>
+  <si>
     <t>Site Director (Queens)</t>
   </si>
   <si>
@@ -1780,6 +2200,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/f70b759f89024c248bbf8fa9c6f97ea8-social-media-manager-651-arts-kings-county</t>
   </si>
   <si>
+    <t>Social Worker, CDP</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73f7d424ba744b1184680bec02646777-social-worker-cdp-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
     <t>Special Events Assisant</t>
   </si>
   <si>
@@ -1795,6 +2224,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/e36549fd59fa445e9c6e78551050b159-special-events-assisant-madison-square-boys-girls-club-foundation-new-york</t>
   </si>
   <si>
+    <t>Special Initiatives Program Officer</t>
+  </si>
+  <si>
+    <t>The David and Lucile Packard Foundation</t>
+  </si>
+  <si>
+    <t>Los Altos, California</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 230000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9f0d26e2ea6f40bea2a988e35150aeec-special-initiatives-program-officer-the-david-and-lucile-packard-foundation-los-altos</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
@@ -1816,9 +2263,6 @@
     <t>The Human Trafficking Legal Center</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e295c800e1214bc0b109055e2e471241-staff-attorney-direct-legal-services-the-human-trafficking-legal-center-washington</t>
   </si>
   <si>
@@ -1861,6 +2305,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/235b0a1b551d4ce698220e8a897e4c8f-synagogue-partnership-social-worker-dorot-new-york</t>
   </si>
   <si>
+    <t>Union Organizer</t>
+  </si>
+  <si>
+    <t>SEIU Local 503, OPEU</t>
+  </si>
+  <si>
+    <t>Pendleton, Oregon</t>
+  </si>
+  <si>
+    <t>USD 79380.00 - 115452.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f364e5ea9e8f413293ffb02f6e9ae3f5-union-organizer-seiu-local-503-opeu-pendleton</t>
+  </si>
+  <si>
+    <t>Vegetable Apprentice</t>
+  </si>
+  <si>
+    <t>Glynwood Center for Regional Food and Farming</t>
+  </si>
+  <si>
+    <t>Cold Spring, New York</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 17.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/05135e4951cb434db844a73b6f21d96d-vegetable-apprentice-glynwood-center-for-regional-food-and-farming-cold-spring</t>
+  </si>
+  <si>
     <t>Vice President of Advancement Operations</t>
   </si>
   <si>
@@ -1873,10 +2347,37 @@
     <t>https://www.idealist.org/en/nonprofit-job/049705f31de04fb8a7ac10f01f5cb0b3-vice-president-of-advancement-operations-jcc-association-new-york</t>
   </si>
   <si>
+    <t>Vice President of Finance and Business Affairs</t>
+  </si>
+  <si>
+    <t>The Partnership for Los Angeles Schools</t>
+  </si>
+  <si>
+    <t>USD 173747.00 - 173747.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20ea2d1539784a6ea71bfcc85336e408-vice-president-of-finance-and-business-affairs-the-partnership-for-los-angeles-schools-los-angeles</t>
+  </si>
+  <si>
     <t>Workforce Community Organizer</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/67bf17abab1b4083a5011a98f6f8eff7-workforce-community-organizer-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Youth Engagement Assistant – AmeriCorps</t>
+  </si>
+  <si>
+    <t>SchoolTalk, Inc.</t>
+  </si>
+  <si>
+    <t>USD 25000.00 - 25000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9290dd8212548089d42b01bc663ffc7-youth-engagement-assistant-americorps-schooltalk-inc-washington</t>
   </si>
 </sst>
 </file>
@@ -3080,7 +3581,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3334,36 +3835,36 @@
         <v>220</v>
       </c>
       <c r="C11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" t="s">
         <v>221</v>
       </c>
-      <c r="D11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E11" t="s">
-        <v>193</v>
-      </c>
       <c r="F11" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
         <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="F12" t="s">
         <v>193</v>
@@ -3380,16 +3881,16 @@
         <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="D13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" t="s">
         <v>230</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>193</v>
-      </c>
-      <c r="F13" t="s">
-        <v>211</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>231</v>
@@ -3412,260 +3913,260 @@
         <v>235</v>
       </c>
       <c r="F14" t="s">
+        <v>193</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" t="s">
         <v>238</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" t="s">
         <v>239</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="D15" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" t="s">
-        <v>242</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
         <v>244</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
         <v>245</v>
       </c>
-      <c r="C16" t="s">
+      <c r="H16" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D16" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" t="s">
-        <v>248</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" t="s">
+        <v>248</v>
+      </c>
+      <c r="C17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" t="s">
         <v>250</v>
       </c>
-      <c r="B17" t="s">
+      <c r="F17" t="s">
         <v>251</v>
       </c>
-      <c r="C17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="H17" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="F17" t="s">
-        <v>253</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>253</v>
+      </c>
+      <c r="B18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" t="s">
         <v>255</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" t="s">
         <v>256</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>257</v>
       </c>
-      <c r="D18" t="s">
-        <v>173</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="H18" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="F18" t="s">
-        <v>259</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>259</v>
+      </c>
+      <c r="B19" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" t="s">
         <v>261</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" t="s">
         <v>262</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>263</v>
       </c>
-      <c r="D19" t="s">
-        <v>173</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="H19" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="F19" t="s">
-        <v>265</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>265</v>
+      </c>
+      <c r="B20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" t="s">
         <v>267</v>
       </c>
-      <c r="B20" t="s">
+      <c r="F20" t="s">
         <v>268</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="D20" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" t="s">
-        <v>270</v>
-      </c>
-      <c r="F20" t="s">
-        <v>271</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" t="s">
         <v>273</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>274</v>
       </c>
-      <c r="C21" t="s">
+      <c r="H21" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="D21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" t="s">
-        <v>276</v>
-      </c>
-      <c r="F21" t="s">
-        <v>277</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>276</v>
+      </c>
+      <c r="B22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" t="s">
         <v>279</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
         <v>280</v>
       </c>
-      <c r="C22" t="s">
+      <c r="H22" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="D22" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" t="s">
-        <v>282</v>
-      </c>
-      <c r="F22" t="s">
-        <v>283</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" t="s">
+        <v>283</v>
+      </c>
+      <c r="C23" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" t="s">
         <v>285</v>
       </c>
-      <c r="B23" t="s">
+      <c r="E23" t="s">
         <v>286</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>287</v>
       </c>
-      <c r="D23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="H23" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="F23" t="s">
-        <v>289</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>289</v>
+      </c>
+      <c r="B24" t="s">
+        <v>290</v>
+      </c>
+      <c r="C24" t="s">
         <v>291</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" t="s">
         <v>292</v>
       </c>
-      <c r="C24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>293</v>
       </c>
-      <c r="E24" t="s">
+      <c r="H24" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="F24" t="s">
-        <v>295</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>295</v>
+      </c>
+      <c r="B25" t="s">
+        <v>296</v>
+      </c>
+      <c r="C25" t="s">
         <v>297</v>
       </c>
-      <c r="B25" t="s">
-        <v>292</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" t="s">
         <v>298</v>
       </c>
-      <c r="D25" t="s">
-        <v>293</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>299</v>
-      </c>
-      <c r="F25" t="s">
-        <v>295</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>300</v>
@@ -3702,352 +4203,352 @@
         <v>308</v>
       </c>
       <c r="C27" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" t="s">
         <v>309</v>
       </c>
-      <c r="D27" t="s">
-        <v>173</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>211</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="F27" t="s">
-        <v>311</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>311</v>
+      </c>
+      <c r="B28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F28" t="s">
         <v>313</v>
       </c>
-      <c r="B28" t="s">
+      <c r="H28" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C28" t="s">
-        <v>225</v>
-      </c>
-      <c r="D28" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" t="s">
-        <v>315</v>
-      </c>
-      <c r="F28" t="s">
-        <v>316</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>311</v>
+      </c>
+      <c r="B29" t="s">
+        <v>315</v>
+      </c>
+      <c r="C29" t="s">
+        <v>316</v>
+      </c>
+      <c r="D29" t="s">
+        <v>317</v>
+      </c>
+      <c r="E29" t="s">
         <v>318</v>
       </c>
-      <c r="B29" t="s">
+      <c r="F29" t="s">
+        <v>313</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="C29" t="s">
-        <v>309</v>
-      </c>
-      <c r="D29" t="s">
-        <v>173</v>
-      </c>
-      <c r="E29" t="s">
-        <v>320</v>
-      </c>
-      <c r="F29" t="s">
-        <v>321</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>320</v>
+      </c>
+      <c r="B30" t="s">
+        <v>321</v>
+      </c>
+      <c r="C30" t="s">
+        <v>322</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
         <v>323</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>324</v>
       </c>
-      <c r="C30" t="s">
+      <c r="H30" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="D30" t="s">
-        <v>173</v>
-      </c>
-      <c r="E30" t="s">
-        <v>326</v>
-      </c>
-      <c r="F30" t="s">
-        <v>327</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" t="s">
+        <v>327</v>
+      </c>
+      <c r="C31" t="s">
+        <v>234</v>
+      </c>
+      <c r="D31" t="s">
+        <v>317</v>
+      </c>
+      <c r="E31" t="s">
+        <v>328</v>
+      </c>
+      <c r="F31" t="s">
         <v>329</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H31" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="C31" t="s">
-        <v>331</v>
-      </c>
-      <c r="D31" t="s">
-        <v>173</v>
-      </c>
-      <c r="E31" t="s">
-        <v>332</v>
-      </c>
-      <c r="F31" t="s">
-        <v>333</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>331</v>
+      </c>
+      <c r="B32" t="s">
+        <v>327</v>
+      </c>
+      <c r="C32" t="s">
+        <v>332</v>
+      </c>
+      <c r="D32" t="s">
+        <v>317</v>
+      </c>
+      <c r="E32" t="s">
+        <v>333</v>
+      </c>
+      <c r="F32" t="s">
         <v>329</v>
       </c>
-      <c r="B32" t="s">
-        <v>286</v>
-      </c>
-      <c r="C32" t="s">
-        <v>287</v>
-      </c>
-      <c r="D32" t="s">
-        <v>173</v>
-      </c>
-      <c r="E32" t="s">
-        <v>335</v>
-      </c>
-      <c r="F32" t="s">
-        <v>336</v>
-      </c>
       <c r="H32" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B33" t="s">
+        <v>336</v>
+      </c>
+      <c r="C33" t="s">
+        <v>337</v>
+      </c>
+      <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
         <v>338</v>
       </c>
-      <c r="B33" t="s">
+      <c r="F33" t="s">
         <v>339</v>
       </c>
-      <c r="C33" t="s">
+      <c r="H33" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="D33" t="s">
-        <v>173</v>
-      </c>
-      <c r="E33" t="s">
-        <v>341</v>
-      </c>
-      <c r="F33" t="s">
-        <v>342</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>341</v>
+      </c>
+      <c r="B34" t="s">
+        <v>342</v>
+      </c>
+      <c r="C34" t="s">
+        <v>343</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
         <v>344</v>
       </c>
-      <c r="B34" t="s">
+      <c r="F34" t="s">
         <v>345</v>
       </c>
-      <c r="C34" t="s">
+      <c r="H34" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D34" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" t="s">
-        <v>347</v>
-      </c>
-      <c r="F34" t="s">
-        <v>348</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>347</v>
+      </c>
+      <c r="B35" t="s">
+        <v>348</v>
+      </c>
+      <c r="C35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>349</v>
+      </c>
+      <c r="F35" t="s">
         <v>350</v>
       </c>
-      <c r="B35" t="s">
+      <c r="H35" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="C35" t="s">
-        <v>352</v>
-      </c>
-      <c r="D35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E35" t="s">
-        <v>353</v>
-      </c>
-      <c r="F35" t="s">
-        <v>354</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>352</v>
+      </c>
+      <c r="B36" t="s">
+        <v>353</v>
+      </c>
+      <c r="C36" t="s">
+        <v>343</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>354</v>
+      </c>
+      <c r="F36" t="s">
+        <v>355</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="B36" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" t="s">
-        <v>225</v>
-      </c>
-      <c r="D36" t="s">
-        <v>358</v>
-      </c>
-      <c r="E36" t="s">
-        <v>359</v>
-      </c>
-      <c r="F36" t="s">
-        <v>360</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>357</v>
+      </c>
+      <c r="B37" t="s">
+        <v>358</v>
+      </c>
+      <c r="C37" t="s">
+        <v>359</v>
+      </c>
+      <c r="D37" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" t="s">
+        <v>360</v>
+      </c>
+      <c r="F37" t="s">
+        <v>361</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="B37" t="s">
-        <v>363</v>
-      </c>
-      <c r="C37" t="s">
-        <v>309</v>
-      </c>
-      <c r="D37" t="s">
-        <v>293</v>
-      </c>
-      <c r="E37" t="s">
-        <v>364</v>
-      </c>
-      <c r="F37" t="s">
-        <v>365</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>363</v>
+      </c>
+      <c r="B38" t="s">
+        <v>364</v>
+      </c>
+      <c r="C38" t="s">
+        <v>365</v>
+      </c>
+      <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>366</v>
+      </c>
+      <c r="F38" t="s">
         <v>367</v>
       </c>
-      <c r="B38" t="s">
+      <c r="H38" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="C38" t="s">
-        <v>369</v>
-      </c>
-      <c r="D38" t="s">
-        <v>173</v>
-      </c>
-      <c r="E38" t="s">
-        <v>370</v>
-      </c>
-      <c r="F38" t="s">
-        <v>371</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="C39" t="s">
-        <v>375</v>
+        <v>322</v>
       </c>
       <c r="D39" t="s">
         <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="F39" t="s">
-        <v>295</v>
+        <v>370</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>374</v>
       </c>
       <c r="D40" t="s">
         <v>173</v>
       </c>
       <c r="E40" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F40" t="s">
-        <v>289</v>
+        <v>376</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s">
+        <v>380</v>
+      </c>
+      <c r="D41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
         <v>381</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
         <v>382</v>
       </c>
-      <c r="D41" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="H41" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="F41" t="s">
-        <v>321</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>384</v>
+      </c>
+      <c r="B42" t="s">
         <v>385</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>386</v>
-      </c>
-      <c r="C42" t="s">
-        <v>309</v>
       </c>
       <c r="D42" t="s">
         <v>173</v>
@@ -4070,1261 +4571,2066 @@
         <v>391</v>
       </c>
       <c r="C43" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="D43" t="s">
-        <v>392</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
         <v>393</v>
       </c>
       <c r="F43" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>359</v>
       </c>
       <c r="D44" t="s">
         <v>173</v>
       </c>
       <c r="E44" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F44" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C45" t="s">
-        <v>402</v>
+        <v>234</v>
       </c>
       <c r="D45" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="E45" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F45" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s">
-        <v>402</v>
+        <v>343</v>
       </c>
       <c r="D46" t="s">
         <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F46" t="s">
-        <v>259</v>
+        <v>410</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C47" t="s">
-        <v>225</v>
+        <v>343</v>
       </c>
       <c r="D47" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="E47" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F47" t="s">
-        <v>193</v>
+        <v>415</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s">
-        <v>308</v>
+        <v>418</v>
       </c>
       <c r="C48" t="s">
-        <v>309</v>
+        <v>419</v>
       </c>
       <c r="D48" t="s">
         <v>173</v>
       </c>
       <c r="E48" t="s">
-        <v>204</v>
+        <v>420</v>
       </c>
       <c r="F48" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B49" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C49" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D49" t="s">
-        <v>392</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="F49" t="s">
-        <v>418</v>
+        <v>329</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D50" t="s">
         <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="F50" t="s">
-        <v>423</v>
+        <v>324</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>345</v>
+        <v>430</v>
       </c>
       <c r="C51" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D51" t="s">
         <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F51" t="s">
-        <v>428</v>
+        <v>355</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>430</v>
+        <v>79</v>
       </c>
       <c r="B52" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="C52" t="s">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="D52" t="s">
         <v>173</v>
       </c>
       <c r="E52" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F52" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B53" t="s">
-        <v>256</v>
+        <v>440</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>441</v>
       </c>
       <c r="D53" t="s">
         <v>173</v>
       </c>
       <c r="E53" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="F53" t="s">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C54" t="s">
-        <v>437</v>
+        <v>343</v>
       </c>
       <c r="D54" t="s">
         <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F54" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C55" t="s">
-        <v>352</v>
+        <v>451</v>
       </c>
       <c r="D55" t="s">
         <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="F55" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s">
+        <v>456</v>
+      </c>
+      <c r="C56" t="s">
+        <v>234</v>
+      </c>
+      <c r="D56" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" t="s">
+        <v>457</v>
+      </c>
+      <c r="F56" t="s">
         <v>447</v>
       </c>
-      <c r="C56" t="s">
-        <v>309</v>
-      </c>
-      <c r="D56" t="s">
-        <v>173</v>
-      </c>
-      <c r="E56" t="s">
-        <v>198</v>
-      </c>
-      <c r="F56" t="s">
-        <v>448</v>
-      </c>
       <c r="H56" s="2" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B57" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C57" t="s">
-        <v>452</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
         <v>173</v>
       </c>
       <c r="E57" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="F57" t="s">
-        <v>193</v>
+        <v>462</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s">
-        <v>280</v>
+        <v>465</v>
       </c>
       <c r="C58" t="s">
-        <v>281</v>
+        <v>466</v>
       </c>
       <c r="D58" t="s">
         <v>173</v>
       </c>
       <c r="E58" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="F58" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B59" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C59" t="s">
-        <v>191</v>
+        <v>466</v>
       </c>
       <c r="D59" t="s">
         <v>173</v>
       </c>
       <c r="E59" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="F59" t="s">
-        <v>461</v>
+        <v>274</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C60" t="s">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="D60" t="s">
         <v>173</v>
       </c>
       <c r="E60" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="F60" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s">
-        <v>468</v>
+        <v>342</v>
       </c>
       <c r="C61" t="s">
-        <v>469</v>
+        <v>343</v>
       </c>
       <c r="D61" t="s">
         <v>173</v>
       </c>
       <c r="E61" t="s">
-        <v>470</v>
+        <v>204</v>
       </c>
       <c r="F61" t="s">
-        <v>471</v>
+        <v>345</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s">
-        <v>286</v>
+        <v>479</v>
       </c>
       <c r="C62" t="s">
-        <v>287</v>
+        <v>480</v>
       </c>
       <c r="D62" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="E62" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="F62" t="s">
-        <v>289</v>
+        <v>482</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="D63" t="s">
         <v>173</v>
       </c>
       <c r="E63" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="F63" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s">
-        <v>482</v>
+        <v>385</v>
       </c>
       <c r="C64" t="s">
-        <v>225</v>
+        <v>490</v>
       </c>
       <c r="D64" t="s">
         <v>173</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
+        <v>491</v>
       </c>
       <c r="F64" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s">
-        <v>486</v>
+        <v>385</v>
       </c>
       <c r="C65" t="s">
-        <v>487</v>
+        <v>386</v>
       </c>
       <c r="D65" t="s">
         <v>173</v>
       </c>
       <c r="E65" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="F65" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s">
-        <v>345</v>
+        <v>497</v>
       </c>
       <c r="C66" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="D66" t="s">
         <v>173</v>
       </c>
       <c r="E66" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F66" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s">
-        <v>496</v>
+        <v>271</v>
       </c>
       <c r="C67" t="s">
-        <v>487</v>
+        <v>272</v>
       </c>
       <c r="D67" t="s">
         <v>173</v>
       </c>
       <c r="E67" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F67" t="s">
-        <v>498</v>
+        <v>274</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C68" t="s">
-        <v>225</v>
+        <v>506</v>
       </c>
       <c r="D68" t="s">
         <v>173</v>
       </c>
       <c r="E68" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="F68" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s">
-        <v>196</v>
+        <v>511</v>
       </c>
       <c r="C69" t="s">
-        <v>197</v>
+        <v>392</v>
       </c>
       <c r="D69" t="s">
         <v>173</v>
       </c>
       <c r="E69" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F69" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C70" t="s">
-        <v>511</v>
+        <v>343</v>
       </c>
       <c r="D70" t="s">
-        <v>392</v>
+        <v>173</v>
       </c>
       <c r="E70" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F70" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s">
-        <v>224</v>
+        <v>520</v>
       </c>
       <c r="C71" t="s">
-        <v>225</v>
+        <v>521</v>
       </c>
       <c r="D71" t="s">
         <v>173</v>
       </c>
       <c r="E71" t="s">
-        <v>226</v>
+        <v>522</v>
       </c>
       <c r="F71" t="s">
         <v>193</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B72" t="s">
-        <v>442</v>
+        <v>525</v>
       </c>
       <c r="C72" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="E72" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F72" t="s">
-        <v>444</v>
+        <v>527</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s">
-        <v>520</v>
+        <v>302</v>
       </c>
       <c r="C73" t="s">
-        <v>521</v>
+        <v>303</v>
       </c>
       <c r="D73" t="s">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="E73" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="F73" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s">
-        <v>345</v>
+        <v>533</v>
       </c>
       <c r="C74" t="s">
-        <v>525</v>
+        <v>191</v>
       </c>
       <c r="D74" t="s">
         <v>173</v>
       </c>
       <c r="E74" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="F74" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s">
-        <v>345</v>
+        <v>538</v>
       </c>
       <c r="C75" t="s">
-        <v>530</v>
+        <v>343</v>
       </c>
       <c r="D75" t="s">
         <v>173</v>
       </c>
       <c r="E75" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="F75" t="s">
-        <v>527</v>
+        <v>211</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B76" t="s">
-        <v>345</v>
+        <v>542</v>
       </c>
       <c r="C76" t="s">
-        <v>426</v>
+        <v>543</v>
       </c>
       <c r="D76" t="s">
         <v>173</v>
       </c>
       <c r="E76" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="F76" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="B77" t="s">
-        <v>345</v>
+        <v>548</v>
       </c>
       <c r="C77" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="E77" t="s">
-        <v>526</v>
+        <v>193</v>
       </c>
       <c r="F77" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="B78" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="C78" t="s">
-        <v>539</v>
+        <v>365</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="E78" t="s">
-        <v>193</v>
+        <v>554</v>
       </c>
       <c r="F78" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="B79" t="s">
-        <v>268</v>
+        <v>558</v>
       </c>
       <c r="C79" t="s">
-        <v>269</v>
+        <v>559</v>
       </c>
       <c r="D79" t="s">
         <v>173</v>
       </c>
       <c r="E79" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="F79" t="s">
-        <v>271</v>
+        <v>561</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="B80" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="C80" t="s">
-        <v>309</v>
+        <v>565</v>
       </c>
       <c r="D80" t="s">
         <v>173</v>
       </c>
       <c r="E80" t="s">
-        <v>198</v>
+        <v>566</v>
       </c>
       <c r="F80" t="s">
-        <v>371</v>
+        <v>567</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B81" t="s">
-        <v>549</v>
+        <v>321</v>
       </c>
       <c r="C81" t="s">
-        <v>225</v>
+        <v>322</v>
       </c>
       <c r="D81" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="E81" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="F81" t="s">
-        <v>551</v>
+        <v>324</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="B82" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D82" t="s">
         <v>173</v>
       </c>
       <c r="E82" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="F82" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="C83" t="s">
-        <v>197</v>
+        <v>332</v>
       </c>
       <c r="D83" t="s">
         <v>173</v>
       </c>
       <c r="E83" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="F83" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="B84" t="s">
-        <v>256</v>
+        <v>578</v>
       </c>
       <c r="C84" t="s">
-        <v>257</v>
+        <v>332</v>
       </c>
       <c r="D84" t="s">
         <v>173</v>
       </c>
       <c r="E84" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="F84" t="s">
-        <v>259</v>
+        <v>580</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C85" t="s">
-        <v>568</v>
+        <v>234</v>
       </c>
       <c r="D85" t="s">
         <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>569</v>
+        <v>298</v>
       </c>
       <c r="F85" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B86" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C86" t="s">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
       <c r="E86" t="s">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="F86" t="s">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="B87" t="s">
-        <v>345</v>
+        <v>595</v>
       </c>
       <c r="C87" t="s">
-        <v>346</v>
+        <v>596</v>
       </c>
       <c r="D87" t="s">
         <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F87" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="B88" t="s">
-        <v>583</v>
+        <v>385</v>
       </c>
       <c r="C88" t="s">
-        <v>584</v>
+        <v>490</v>
       </c>
       <c r="D88" t="s">
-        <v>293</v>
+        <v>173</v>
       </c>
       <c r="E88" t="s">
-        <v>585</v>
+        <v>221</v>
       </c>
       <c r="F88" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="B89" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="C89" t="s">
-        <v>225</v>
+        <v>596</v>
       </c>
       <c r="D89" t="s">
         <v>173</v>
       </c>
       <c r="E89" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="F89" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="B90" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="C90" t="s">
-        <v>225</v>
+        <v>610</v>
       </c>
       <c r="D90" t="s">
         <v>173</v>
       </c>
       <c r="E90" t="s">
-        <v>478</v>
+        <v>193</v>
       </c>
       <c r="F90" t="s">
-        <v>489</v>
+        <v>611</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="B91" t="s">
-        <v>401</v>
+        <v>614</v>
       </c>
       <c r="C91" t="s">
-        <v>402</v>
+        <v>615</v>
       </c>
       <c r="D91" t="s">
         <v>173</v>
       </c>
       <c r="E91" t="s">
-        <v>347</v>
+        <v>616</v>
       </c>
       <c r="F91" t="s">
-        <v>259</v>
+        <v>617</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="C92" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="D92" t="s">
         <v>173</v>
       </c>
       <c r="E92" t="s">
-        <v>198</v>
+        <v>621</v>
       </c>
       <c r="F92" t="s">
-        <v>600</v>
+        <v>622</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>601</v>
+        <v>623</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="B93" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="C93" t="s">
-        <v>197</v>
+        <v>392</v>
       </c>
       <c r="D93" t="s">
         <v>173</v>
       </c>
       <c r="E93" t="s">
-        <v>198</v>
+        <v>626</v>
       </c>
       <c r="F93" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>604</v>
+        <v>628</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>605</v>
+        <v>629</v>
       </c>
       <c r="B94" t="s">
-        <v>606</v>
+        <v>196</v>
       </c>
       <c r="C94" t="s">
-        <v>287</v>
+        <v>197</v>
       </c>
       <c r="D94" t="s">
         <v>173</v>
       </c>
       <c r="E94" t="s">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="F94" t="s">
-        <v>608</v>
+        <v>631</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>609</v>
+        <v>632</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="B95" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="C95" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D95" t="s">
         <v>173</v>
       </c>
       <c r="E95" t="s">
-        <v>612</v>
+        <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="C96" t="s">
-        <v>298</v>
+        <v>638</v>
       </c>
       <c r="D96" t="s">
         <v>173</v>
       </c>
       <c r="E96" t="s">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="F96" t="s">
-        <v>193</v>
+        <v>287</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>619</v>
+        <v>641</v>
       </c>
       <c r="B97" t="s">
-        <v>280</v>
+        <v>642</v>
       </c>
       <c r="C97" t="s">
-        <v>281</v>
+        <v>643</v>
       </c>
       <c r="D97" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="E97" t="s">
-        <v>456</v>
+        <v>193</v>
       </c>
       <c r="F97" t="s">
-        <v>283</v>
+        <v>644</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>620</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>646</v>
+      </c>
+      <c r="B98" t="s">
+        <v>233</v>
+      </c>
+      <c r="C98" t="s">
+        <v>234</v>
+      </c>
+      <c r="D98" t="s">
+        <v>173</v>
+      </c>
+      <c r="E98" t="s">
+        <v>235</v>
+      </c>
+      <c r="F98" t="s">
+        <v>193</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>648</v>
+      </c>
+      <c r="B99" t="s">
+        <v>511</v>
+      </c>
+      <c r="C99" t="s">
+        <v>392</v>
+      </c>
+      <c r="D99" t="s">
+        <v>173</v>
+      </c>
+      <c r="E99" t="s">
+        <v>649</v>
+      </c>
+      <c r="F99" t="s">
+        <v>513</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>651</v>
+      </c>
+      <c r="B100" t="s">
+        <v>652</v>
+      </c>
+      <c r="C100" t="s">
+        <v>653</v>
+      </c>
+      <c r="D100" t="s">
+        <v>403</v>
+      </c>
+      <c r="E100" t="s">
+        <v>654</v>
+      </c>
+      <c r="F100" t="s">
+        <v>405</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>656</v>
+      </c>
+      <c r="B101" t="s">
+        <v>385</v>
+      </c>
+      <c r="C101" t="s">
+        <v>657</v>
+      </c>
+      <c r="D101" t="s">
+        <v>173</v>
+      </c>
+      <c r="E101" t="s">
+        <v>658</v>
+      </c>
+      <c r="F101" t="s">
+        <v>659</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>661</v>
+      </c>
+      <c r="B102" t="s">
+        <v>385</v>
+      </c>
+      <c r="C102" t="s">
+        <v>662</v>
+      </c>
+      <c r="D102" t="s">
+        <v>173</v>
+      </c>
+      <c r="E102" t="s">
+        <v>658</v>
+      </c>
+      <c r="F102" t="s">
+        <v>659</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>664</v>
+      </c>
+      <c r="B103" t="s">
+        <v>385</v>
+      </c>
+      <c r="C103" t="s">
+        <v>490</v>
+      </c>
+      <c r="D103" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" t="s">
+        <v>658</v>
+      </c>
+      <c r="F103" t="s">
+        <v>659</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>666</v>
+      </c>
+      <c r="B104" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" t="s">
+        <v>667</v>
+      </c>
+      <c r="D104" t="s">
+        <v>173</v>
+      </c>
+      <c r="E104" t="s">
+        <v>658</v>
+      </c>
+      <c r="F104" t="s">
+        <v>659</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>669</v>
+      </c>
+      <c r="B105" t="s">
+        <v>670</v>
+      </c>
+      <c r="C105" t="s">
+        <v>671</v>
+      </c>
+      <c r="D105" t="s">
+        <v>173</v>
+      </c>
+      <c r="E105" t="s">
+        <v>193</v>
+      </c>
+      <c r="F105" t="s">
+        <v>672</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>674</v>
+      </c>
+      <c r="B106" t="s">
+        <v>290</v>
+      </c>
+      <c r="C106" t="s">
+        <v>291</v>
+      </c>
+      <c r="D106" t="s">
+        <v>173</v>
+      </c>
+      <c r="E106" t="s">
+        <v>675</v>
+      </c>
+      <c r="F106" t="s">
+        <v>293</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>677</v>
+      </c>
+      <c r="B107" t="s">
+        <v>678</v>
+      </c>
+      <c r="C107" t="s">
+        <v>343</v>
+      </c>
+      <c r="D107" t="s">
+        <v>173</v>
+      </c>
+      <c r="E107" t="s">
+        <v>198</v>
+      </c>
+      <c r="F107" t="s">
+        <v>287</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>680</v>
+      </c>
+      <c r="B108" t="s">
+        <v>681</v>
+      </c>
+      <c r="C108" t="s">
+        <v>682</v>
+      </c>
+      <c r="D108" t="s">
+        <v>173</v>
+      </c>
+      <c r="E108" t="s">
+        <v>244</v>
+      </c>
+      <c r="F108" t="s">
+        <v>683</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>685</v>
+      </c>
+      <c r="B109" t="s">
+        <v>686</v>
+      </c>
+      <c r="C109" t="s">
+        <v>234</v>
+      </c>
+      <c r="D109" t="s">
+        <v>173</v>
+      </c>
+      <c r="E109" t="s">
+        <v>687</v>
+      </c>
+      <c r="F109" t="s">
+        <v>688</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>690</v>
+      </c>
+      <c r="B110" t="s">
+        <v>691</v>
+      </c>
+      <c r="C110" t="s">
+        <v>197</v>
+      </c>
+      <c r="D110" t="s">
+        <v>173</v>
+      </c>
+      <c r="E110" t="s">
+        <v>692</v>
+      </c>
+      <c r="F110" t="s">
+        <v>693</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>695</v>
+      </c>
+      <c r="B111" t="s">
+        <v>696</v>
+      </c>
+      <c r="C111" t="s">
+        <v>197</v>
+      </c>
+      <c r="D111" t="s">
+        <v>173</v>
+      </c>
+      <c r="E111" t="s">
+        <v>697</v>
+      </c>
+      <c r="F111" t="s">
+        <v>698</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>700</v>
+      </c>
+      <c r="B112" t="s">
+        <v>271</v>
+      </c>
+      <c r="C112" t="s">
+        <v>272</v>
+      </c>
+      <c r="D112" t="s">
+        <v>173</v>
+      </c>
+      <c r="E112" t="s">
+        <v>701</v>
+      </c>
+      <c r="F112" t="s">
+        <v>274</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>703</v>
+      </c>
+      <c r="B113" t="s">
+        <v>704</v>
+      </c>
+      <c r="C113" t="s">
+        <v>705</v>
+      </c>
+      <c r="D113" t="s">
+        <v>173</v>
+      </c>
+      <c r="E113" t="s">
+        <v>706</v>
+      </c>
+      <c r="F113" t="s">
+        <v>707</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>709</v>
+      </c>
+      <c r="B114" t="s">
+        <v>710</v>
+      </c>
+      <c r="C114" t="s">
+        <v>711</v>
+      </c>
+      <c r="D114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E114" t="s">
+        <v>712</v>
+      </c>
+      <c r="F114" t="s">
+        <v>713</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>715</v>
+      </c>
+      <c r="B115" t="s">
+        <v>625</v>
+      </c>
+      <c r="C115" t="s">
+        <v>392</v>
+      </c>
+      <c r="D115" t="s">
+        <v>173</v>
+      </c>
+      <c r="E115" t="s">
+        <v>716</v>
+      </c>
+      <c r="F115" t="s">
+        <v>627</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>718</v>
+      </c>
+      <c r="B116" t="s">
+        <v>385</v>
+      </c>
+      <c r="C116" t="s">
+        <v>386</v>
+      </c>
+      <c r="D116" t="s">
+        <v>173</v>
+      </c>
+      <c r="E116" t="s">
+        <v>719</v>
+      </c>
+      <c r="F116" t="s">
+        <v>720</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>722</v>
+      </c>
+      <c r="B117" t="s">
+        <v>723</v>
+      </c>
+      <c r="C117" t="s">
+        <v>724</v>
+      </c>
+      <c r="D117" t="s">
+        <v>317</v>
+      </c>
+      <c r="E117" t="s">
+        <v>725</v>
+      </c>
+      <c r="F117" t="s">
+        <v>726</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>728</v>
+      </c>
+      <c r="B118" t="s">
+        <v>379</v>
+      </c>
+      <c r="C118" t="s">
+        <v>380</v>
+      </c>
+      <c r="D118" t="s">
+        <v>173</v>
+      </c>
+      <c r="E118" t="s">
+        <v>729</v>
+      </c>
+      <c r="F118" t="s">
+        <v>382</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>731</v>
+      </c>
+      <c r="B119" t="s">
+        <v>732</v>
+      </c>
+      <c r="C119" t="s">
+        <v>234</v>
+      </c>
+      <c r="D119" t="s">
+        <v>173</v>
+      </c>
+      <c r="E119" t="s">
+        <v>733</v>
+      </c>
+      <c r="F119" t="s">
+        <v>734</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>736</v>
+      </c>
+      <c r="B120" t="s">
+        <v>737</v>
+      </c>
+      <c r="C120" t="s">
+        <v>738</v>
+      </c>
+      <c r="D120" t="s">
+        <v>173</v>
+      </c>
+      <c r="E120" t="s">
+        <v>739</v>
+      </c>
+      <c r="F120" t="s">
+        <v>740</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>742</v>
+      </c>
+      <c r="B121" t="s">
+        <v>743</v>
+      </c>
+      <c r="C121" t="s">
+        <v>234</v>
+      </c>
+      <c r="D121" t="s">
+        <v>173</v>
+      </c>
+      <c r="E121" t="s">
+        <v>574</v>
+      </c>
+      <c r="F121" t="s">
+        <v>598</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>745</v>
+      </c>
+      <c r="B122" t="s">
+        <v>465</v>
+      </c>
+      <c r="C122" t="s">
+        <v>466</v>
+      </c>
+      <c r="D122" t="s">
+        <v>173</v>
+      </c>
+      <c r="E122" t="s">
+        <v>387</v>
+      </c>
+      <c r="F122" t="s">
+        <v>274</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>747</v>
+      </c>
+      <c r="B123" t="s">
+        <v>748</v>
+      </c>
+      <c r="C123" t="s">
+        <v>197</v>
+      </c>
+      <c r="D123" t="s">
+        <v>173</v>
+      </c>
+      <c r="E123" t="s">
+        <v>198</v>
+      </c>
+      <c r="F123" t="s">
+        <v>410</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>750</v>
+      </c>
+      <c r="B124" t="s">
+        <v>748</v>
+      </c>
+      <c r="C124" t="s">
+        <v>197</v>
+      </c>
+      <c r="D124" t="s">
+        <v>173</v>
+      </c>
+      <c r="E124" t="s">
+        <v>198</v>
+      </c>
+      <c r="F124" t="s">
+        <v>751</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>753</v>
+      </c>
+      <c r="B125" t="s">
+        <v>754</v>
+      </c>
+      <c r="C125" t="s">
+        <v>322</v>
+      </c>
+      <c r="D125" t="s">
+        <v>173</v>
+      </c>
+      <c r="E125" t="s">
+        <v>755</v>
+      </c>
+      <c r="F125" t="s">
+        <v>756</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>758</v>
+      </c>
+      <c r="B126" t="s">
+        <v>759</v>
+      </c>
+      <c r="C126" t="s">
+        <v>234</v>
+      </c>
+      <c r="D126" t="s">
+        <v>173</v>
+      </c>
+      <c r="E126" t="s">
+        <v>760</v>
+      </c>
+      <c r="F126" t="s">
+        <v>761</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>763</v>
+      </c>
+      <c r="B127" t="s">
+        <v>764</v>
+      </c>
+      <c r="C127" t="s">
+        <v>765</v>
+      </c>
+      <c r="D127" t="s">
+        <v>173</v>
+      </c>
+      <c r="E127" t="s">
+        <v>766</v>
+      </c>
+      <c r="F127" t="s">
+        <v>178</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>768</v>
+      </c>
+      <c r="B128" t="s">
+        <v>769</v>
+      </c>
+      <c r="C128" t="s">
+        <v>770</v>
+      </c>
+      <c r="D128" t="s">
+        <v>173</v>
+      </c>
+      <c r="E128" t="s">
+        <v>771</v>
+      </c>
+      <c r="F128" t="s">
+        <v>193</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>773</v>
+      </c>
+      <c r="B129" t="s">
+        <v>774</v>
+      </c>
+      <c r="C129" t="s">
+        <v>332</v>
+      </c>
+      <c r="D129" t="s">
+        <v>173</v>
+      </c>
+      <c r="E129" t="s">
+        <v>775</v>
+      </c>
+      <c r="F129" t="s">
+        <v>193</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>777</v>
+      </c>
+      <c r="B130" t="s">
+        <v>778</v>
+      </c>
+      <c r="C130" t="s">
+        <v>63</v>
+      </c>
+      <c r="D130" t="s">
+        <v>173</v>
+      </c>
+      <c r="E130" t="s">
+        <v>779</v>
+      </c>
+      <c r="F130" t="s">
+        <v>598</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>781</v>
+      </c>
+      <c r="B131" t="s">
+        <v>302</v>
+      </c>
+      <c r="C131" t="s">
+        <v>303</v>
+      </c>
+      <c r="D131" t="s">
+        <v>173</v>
+      </c>
+      <c r="E131" t="s">
+        <v>530</v>
+      </c>
+      <c r="F131" t="s">
+        <v>305</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>783</v>
+      </c>
+      <c r="B132" t="s">
+        <v>784</v>
+      </c>
+      <c r="C132" t="s">
+        <v>197</v>
+      </c>
+      <c r="D132" t="s">
+        <v>403</v>
+      </c>
+      <c r="E132" t="s">
+        <v>785</v>
+      </c>
+      <c r="F132" t="s">
+        <v>786</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -5426,6 +6732,41 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
